--- a/outputs/plan/план_продаж_октябрь_2026_по_группам.xlsx
+++ b/outputs/plan/план_продаж_октябрь_2026_по_группам.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,10 +78,9 @@
       <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
-    <font/>
     <font>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -168,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,17 +175,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -576,8 +574,8 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -586,14 +584,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ДАШБОРД — ПЛАН ПРОДАЖ ОКТЯБРЬ 2026 (магазин Коротич)</t>
+          <t>ДАШБОРД — ПЛАН ПРОДАЖ ОКТЯБРЬ 2026 (Коротич)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Сегодня 01.10.2026. План от факта Ракеты. 3 группы: Косметика / Деды Морозы / Электроника.</t>
+          <t>База — факт окт-2025 из Ракеты (сезонно корректно, СПП восстановлен). Сегодня 01.10.2026.</t>
         </is>
       </c>
     </row>
@@ -634,19 +632,19 @@
         <v>107901</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>9258</v>
+        <v>16768</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>9512287</v>
+        <v>18635536</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1629530</v>
+        <v>3273713</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>ДЕДЫ МОРОЗЫ</t>
+          <t>ДЕДЫ МОРОЗЫ (старт сезона)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
@@ -689,31 +687,33 @@
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="8" t="n">
-        <v>10514</v>
-      </c>
-      <c r="D8" s="7" t="n"/>
+        <v>18024</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>20295590</v>
+      </c>
       <c r="E8" s="8" t="n">
-        <v>2062480</v>
+        <v>3706663</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>ИТОГО ПЛАН ПРИБЫЛИ ОКТЯБРЬ: 2.06 млн ₽</t>
+          <t>ИТОГО ПЛАН ПРИБЫЛИ ОКТЯБРЬ: 3.71 млн ₽   |   выручка 20.30 млн ₽</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Косметика 1.63 млн · Деды Морозы 433 тыс (старт, пик ноя-дек) · Электроника — распродажа</t>
+          <t>Сезонность (факт прошлого года): окт 17,9к → ноя 26,9к → дек 55,1к шт. Главный рост — ноябрь-декабрь.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Листы: «Косметика по брендам» (каждый товар) · «Деды Морозы» · «Электроника»</t>
+          <t>Листы: Косметика по брендам · Деды Морозы · Электроника</t>
         </is>
       </c>
     </row>
@@ -731,30 +731,30 @@
   <dimension ref="A1:K155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>КОСМЕТИКА — ПЛАН ОКТЯБРЬ ПО БРЕНДАМ (каждый товар)</t>
+          <t>КОСМЕТИКА — ПЛАН ОКТЯБРЬ 2026 ПО БРЕНДАМ (сезонная база = факт окт-2025)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Продажи — факт Ракеты. ПЛАН = факт×1,5 (СПП вернулся+сезон), не больше остатка. Маржа — при цене под ROI≥30%.</t>
+          <t>База плана — фактические продажи окт-2025 из Ракеты (СПП вернулся, сезон тот же). Ограничено остатком. Маржа при цене под ROI≥30%.</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Продажи/мес факт</t>
+          <t>Окт-2025 факт шт</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Запас мес</t>
+          <t>Сред.норм/мес</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>ПЛАН окт шт</t>
+          <t>ПЛАН окт-2026 шт</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -841,62 +841,62 @@
       <c r="B6" s="14" t="n">
         <v>204258828</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="5" t="n">
         <v>218</v>
       </c>
-      <c r="D6" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="G6" s="15" t="n">
+      <c r="D6" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>925</v>
       </c>
-      <c r="H6" s="15" t="n">
+      <c r="H6" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="I6" s="15" t="n">
-        <v>16650</v>
-      </c>
-      <c r="J6" s="15" t="n">
-        <v>2538</v>
+      <c r="I6" s="5" t="n">
+        <v>14800</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>2256</v>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ИТОГО COSRX</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="18" t="n">
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="17" t="n">
         <v>218</v>
       </c>
-      <c r="D7" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="G7" s="17" t="n"/>
-      <c r="H7" s="17" t="n"/>
-      <c r="I7" s="18" t="n">
-        <v>16650</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>2538</v>
-      </c>
-      <c r="K7" s="17" t="n"/>
+      <c r="D7" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="17" t="n">
+        <v>14800</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>2256</v>
+      </c>
+      <c r="K7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -924,68 +924,68 @@
       <c r="B9" s="14" t="n">
         <v>608841921</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="5" t="n">
         <v>297</v>
       </c>
-      <c r="D9" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="G9" s="15" t="n">
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G9" s="5" t="n">
         <v>613</v>
       </c>
-      <c r="H9" s="15" t="n">
+      <c r="H9" s="5" t="n">
         <v>176</v>
       </c>
-      <c r="I9" s="15" t="n">
-        <v>15938</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>4576</v>
+      <c r="I9" s="5" t="n">
+        <v>33715</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>9680</v>
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягкая упаковка с колпачком,Шампунь с черным чесноком против выпадения волос</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягкая упаковка Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>608624295</v>
-      </c>
-      <c r="C10" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>925</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>160</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>10175</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>1760</v>
+        <v>608837066</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>924</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>229</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>36036</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>8931</v>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
@@ -996,68 +996,68 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягкая упаковка Шампунь с черным чесноком против выпадения волос</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягкая упаковка с колпачком,Шампунь с черным чесноком против выпадения волос</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>608837066</v>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>59</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>924</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>229</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>5544</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>1374</v>
+        <v>608624295</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>925</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>10175</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>1760</v>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Ограничено остатком</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>ИТОГО DEOPROCE/DEOPROCE-SHAMPOO</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="18" t="n">
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="17" t="n">
         <v>367</v>
       </c>
-      <c r="D12" s="18" t="n">
-        <v>37</v>
-      </c>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="18" t="n">
-        <v>43</v>
-      </c>
-      <c r="G12" s="17" t="n"/>
-      <c r="H12" s="17" t="n"/>
-      <c r="I12" s="18" t="n">
-        <v>31657</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>7710</v>
-      </c>
-      <c r="K12" s="17" t="n"/>
+      <c r="D12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="17" t="n">
+        <v>105</v>
+      </c>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="17" t="n">
+        <v>79926</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>20371</v>
+      </c>
+      <c r="K12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -1085,62 +1085,62 @@
       <c r="B14" s="14" t="n">
         <v>214305722</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="5" t="n">
         <v>395</v>
       </c>
-      <c r="D14" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>39</v>
-      </c>
-      <c r="G14" s="15" t="n">
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="G14" s="5" t="n">
         <v>1964</v>
       </c>
-      <c r="H14" s="15" t="n">
+      <c r="H14" s="5" t="n">
         <v>354</v>
       </c>
-      <c r="I14" s="15" t="n">
-        <v>76596</v>
-      </c>
-      <c r="J14" s="15" t="n">
-        <v>13806</v>
+      <c r="I14" s="5" t="n">
+        <v>184616</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>33276</v>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>ИТОГО DEOPROCE/НАБОР ШАМПУНЬ+БАЛЬЗАМ</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="18" t="n">
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="17" t="n">
         <v>395</v>
       </c>
-      <c r="D15" s="18" t="n">
-        <v>26</v>
-      </c>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="18" t="n">
-        <v>39</v>
-      </c>
-      <c r="G15" s="17" t="n"/>
-      <c r="H15" s="17" t="n"/>
-      <c r="I15" s="18" t="n">
-        <v>76596</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>13806</v>
-      </c>
-      <c r="K15" s="17" t="n"/>
+      <c r="D15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="17" t="n">
+        <v>94</v>
+      </c>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+      <c r="I15" s="17" t="n">
+        <v>184616</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>33276</v>
+      </c>
+      <c r="K15" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -1168,29 +1168,29 @@
       <c r="B17" s="14" t="n">
         <v>207796350</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="5" t="n">
         <v>340</v>
       </c>
-      <c r="D17" s="15" t="n">
-        <v>57</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>86</v>
-      </c>
-      <c r="G17" s="15" t="n">
+      <c r="D17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5" t="n">
         <v>717</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="5" t="n">
         <v>129</v>
       </c>
-      <c r="I17" s="15" t="n">
-        <v>61662</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>11094</v>
+      <c r="I17" s="5" t="n">
+        <v>8604</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>1548</v>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
@@ -1207,62 +1207,62 @@
       <c r="B18" s="14" t="n">
         <v>206058262</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="15" t="n">
+      <c r="D18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="5" t="n">
         <v>1235</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="I18" s="15" t="n">
-        <v>2470</v>
-      </c>
-      <c r="J18" s="15" t="n">
-        <v>484</v>
+      <c r="I18" s="5" t="n">
+        <v>3705</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>726</v>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>ИТОГО ELIZAVECCA</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="18" t="n">
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="17" t="n">
         <v>390</v>
       </c>
-      <c r="D19" s="18" t="n">
-        <v>58</v>
-      </c>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="18" t="n">
-        <v>88</v>
-      </c>
-      <c r="G19" s="17" t="n"/>
-      <c r="H19" s="17" t="n"/>
-      <c r="I19" s="18" t="n">
-        <v>64132</v>
-      </c>
-      <c r="J19" s="18" t="n">
-        <v>11578</v>
-      </c>
-      <c r="K19" s="17" t="n"/>
+      <c r="D19" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="17" t="n">
+        <v>12309</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>2274</v>
+      </c>
+      <c r="K19" s="16" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -1282,158 +1282,158 @@
       <c r="K20" s="13" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B21" s="18" t="n">
         <v>238415286</v>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="19" t="n">
         <v>6400</v>
       </c>
-      <c r="D21" s="20" t="n">
-        <v>774</v>
+      <c r="D21" s="19" t="n">
+        <v>2026</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="F21" s="20" t="n">
-        <v>1161</v>
-      </c>
-      <c r="G21" s="20" t="n">
+        <v>1392</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G21" s="19" t="n">
         <v>614</v>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H21" s="19" t="n">
         <v>156</v>
       </c>
-      <c r="I21" s="20" t="n">
-        <v>712854</v>
-      </c>
-      <c r="J21" s="20" t="n">
-        <v>181116</v>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
-        <is>
-          <t>Затоварка — акцент рекламы</t>
+      <c r="I21" s="19" t="n">
+        <v>1243964</v>
+      </c>
+      <c r="J21" s="19" t="n">
+        <v>316056</v>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>★ Драйвер</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13] / Тональный крем с муцином улитки 13 тон</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="B22" s="14" t="n">
-        <v>207796789</v>
-      </c>
-      <c r="C22" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="D22" s="15" t="n">
-        <v>121</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>182</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>717</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>137</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>130494</v>
-      </c>
-      <c r="J22" s="15" t="n">
-        <v>24934</v>
+        <v>238416010</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>254</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>254</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>510</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>129540</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>17272</v>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>Рабочий</t>
+          <t>Ограничено остатком</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundation [Tone 21] / Тональный крем с пептидами 21 тон</t>
+          <t>ENOUGH - Collagen Moisture Foundation [Tone 13] / Тональный крем для лица с коллагеном 13 тон</t>
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>170198337</v>
-      </c>
-      <c r="C23" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="D23" s="15" t="n">
-        <v>105</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="G23" s="15" t="n">
-        <v>924</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>203</v>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v>21252</v>
-      </c>
-      <c r="J23" s="15" t="n">
-        <v>4669</v>
+        <v>150925321</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>263</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>822</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>221</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>43566</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>11713</v>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>Рабочий</t>
+          <t>Ограничено остатком</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21] / Тональный крем с муцином улитки 21 тон</t>
+          <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundation [Tone 21] / Тональный крем с пептидами 21 тон</t>
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>207796898</v>
-      </c>
-      <c r="C24" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="D24" s="15" t="n">
-        <v>101</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>152</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>718</v>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>104</v>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v>109136</v>
-      </c>
-      <c r="J24" s="15" t="n">
-        <v>15808</v>
+        <v>170198337</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>924</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>21252</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>4669</v>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>Рабочий</t>
+          <t>Ограничено остатком</t>
         </is>
       </c>
     </row>
@@ -1446,29 +1446,29 @@
       <c r="B25" s="14" t="n">
         <v>212889025</v>
       </c>
-      <c r="C25" s="15" t="n">
+      <c r="C25" s="5" t="n">
         <v>352</v>
       </c>
-      <c r="D25" s="15" t="n">
-        <v>101</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F25" s="15" t="n">
-        <v>152</v>
-      </c>
-      <c r="G25" s="15" t="n">
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="G25" s="5" t="n">
         <v>822</v>
       </c>
-      <c r="H25" s="15" t="n">
+      <c r="H25" s="5" t="n">
         <v>270</v>
       </c>
-      <c r="I25" s="15" t="n">
-        <v>124944</v>
-      </c>
-      <c r="J25" s="15" t="n">
-        <v>41040</v>
+      <c r="I25" s="5" t="n">
+        <v>83844</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>27540</v>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
@@ -1479,35 +1479,35 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Foundation [Tone 13] / Тональный крем для лица с коллагеном 13 тон</t>
+          <t>ENOUGH - Collagen Moisture Foundation [Tone 21] / Тональный крем для лица с коллагеном 21 тон</t>
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>150925321</v>
-      </c>
-      <c r="C26" s="15" t="n">
-        <v>53</v>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>53</v>
-      </c>
-      <c r="G26" s="15" t="n">
+        <v>150925322</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="G26" s="5" t="n">
         <v>822</v>
       </c>
-      <c r="H26" s="15" t="n">
-        <v>221</v>
-      </c>
-      <c r="I26" s="15" t="n">
-        <v>43566</v>
-      </c>
-      <c r="J26" s="15" t="n">
-        <v>11713</v>
+      <c r="H26" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>75624</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>17940</v>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
@@ -1518,35 +1518,35 @@
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="B27" s="14" t="n">
-        <v>238416010</v>
-      </c>
-      <c r="C27" s="15" t="n">
-        <v>254</v>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>87</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="G27" s="15" t="n">
-        <v>510</v>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>68</v>
-      </c>
-      <c r="I27" s="15" t="n">
-        <v>66300</v>
-      </c>
-      <c r="J27" s="15" t="n">
-        <v>8840</v>
+        <v>212889027</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>539</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>822</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>56718</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>18561</v>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
@@ -1557,35 +1557,35 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Foundation [Tone 21] / Тональный крем для лица с коллагеном 21 тон</t>
+          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [Tone 21] / Тональный крем с частичками золота 21 тон</t>
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>150925322</v>
-      </c>
-      <c r="C28" s="15" t="n">
-        <v>198</v>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>79</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>118</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>822</v>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v>195</v>
-      </c>
-      <c r="I28" s="15" t="n">
-        <v>96996</v>
-      </c>
-      <c r="J28" s="15" t="n">
-        <v>23010</v>
+        <v>170198109</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>718</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>45234</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>7182</v>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
@@ -1596,74 +1596,74 @@
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>ENOUGH - Collagen Moisture BB Cream SPF47 PA+++ [50ml] / Увлажняющий BB крем с коллагеном</t>
         </is>
       </c>
       <c r="B29" s="14" t="n">
-        <v>212889027</v>
-      </c>
-      <c r="C29" s="15" t="n">
-        <v>539</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>39</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>58</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>822</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>269</v>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>47676</v>
-      </c>
-      <c r="J29" s="15" t="n">
-        <v>15602</v>
+        <v>238413828</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>687</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>527</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>32674</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>4278</v>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen 3in1 Whitening Moisture Foundation [Tone 21] / Тональный крем для лица с коллагеном 3в1 [21 тон]</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13] / Тональный крем с муцином улитки 13 тон</t>
         </is>
       </c>
       <c r="B30" s="14" t="n">
-        <v>151132052</v>
-      </c>
-      <c r="C30" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>718</v>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>149</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>8616</v>
-      </c>
-      <c r="J30" s="15" t="n">
-        <v>1788</v>
+        <v>207796789</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>298</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>717</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>37284</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>7124</v>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
@@ -1680,150 +1680,150 @@
       <c r="B31" s="14" t="n">
         <v>212889028</v>
       </c>
-      <c r="C31" s="15" t="n">
+      <c r="C31" s="5" t="n">
         <v>694</v>
       </c>
-      <c r="D31" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="G31" s="15" t="n">
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="G31" s="5" t="n">
         <v>822</v>
       </c>
-      <c r="H31" s="15" t="n">
+      <c r="H31" s="5" t="n">
         <v>252</v>
       </c>
-      <c r="I31" s="15" t="n">
-        <v>18084</v>
-      </c>
-      <c r="J31" s="15" t="n">
-        <v>5544</v>
+      <c r="I31" s="5" t="n">
+        <v>37812</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>11592</v>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture BB Cream SPF47 PA+++ [50ml] / Увлажняющий BB крем с коллагеном</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21] / Тональный крем с муцином улитки 21 тон</t>
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>238413828</v>
-      </c>
-      <c r="C32" s="15" t="n">
-        <v>687</v>
-      </c>
-      <c r="D32" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="F32" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="G32" s="15" t="n">
-        <v>527</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>69</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>10540</v>
-      </c>
-      <c r="J32" s="15" t="n">
-        <v>1380</v>
+        <v>207796898</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>718</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>25130</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>3640</v>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [Tone 13] / Тональный крем с частичками золота 13 тон</t>
+          <t>ENOUGH - Collagen 3in1 Whitening Moisture Foundation [Tone 21] / Тональный крем для лица с коллагеном 3в1 [21 тон]</t>
         </is>
       </c>
       <c r="B33" s="14" t="n">
-        <v>170198180</v>
-      </c>
-      <c r="C33" s="15" t="n">
-        <v>200</v>
-      </c>
-      <c r="D33" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="F33" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G33" s="15" t="n">
+        <v>151132052</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G33" s="5" t="n">
         <v>718</v>
       </c>
-      <c r="H33" s="15" t="n">
-        <v>116</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>7180</v>
-      </c>
-      <c r="J33" s="15" t="n">
-        <v>1160</v>
+      <c r="H33" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>8616</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>1788</v>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Ограничено остатком</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [Tone 21] / Тональный крем с частичками золота 21 тон</t>
+          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [Tone 13] / Тональный крем с частичками золота 13 тон</t>
         </is>
       </c>
       <c r="B34" s="14" t="n">
-        <v>170198109</v>
-      </c>
-      <c r="C34" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="D34" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="F34" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="G34" s="15" t="n">
+        <v>170198180</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G34" s="5" t="n">
         <v>718</v>
       </c>
-      <c r="H34" s="15" t="n">
-        <v>114</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>5744</v>
-      </c>
-      <c r="J34" s="15" t="n">
-        <v>912</v>
+      <c r="H34" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>17232</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>2784</v>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       <c r="B35" s="14" t="n">
         <v>170198835</v>
       </c>
-      <c r="C35" s="15" t="n">
+      <c r="C35" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="D35" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>200</v>
-      </c>
-      <c r="F35" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="G35" s="15" t="n">
+      <c r="D35" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" s="5" t="n">
         <v>776</v>
       </c>
-      <c r="H35" s="15" t="n">
+      <c r="H35" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="I35" s="15" t="n">
-        <v>6208</v>
-      </c>
-      <c r="J35" s="15" t="n">
-        <v>760</v>
+      <c r="I35" s="5" t="n">
+        <v>7760</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>950</v>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>ИТОГО ENOUGH</t>
         </is>
       </c>
-      <c r="B36" s="17" t="n"/>
-      <c r="C36" s="18" t="n">
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="17" t="n">
         <v>11912</v>
       </c>
-      <c r="D36" s="18" t="n">
-        <v>1578</v>
-      </c>
-      <c r="E36" s="17" t="n"/>
-      <c r="F36" s="18" t="n">
-        <v>2109</v>
-      </c>
-      <c r="G36" s="17" t="n"/>
-      <c r="H36" s="17" t="n"/>
-      <c r="I36" s="18" t="n">
-        <v>1409590</v>
-      </c>
-      <c r="J36" s="18" t="n">
-        <v>338276</v>
-      </c>
-      <c r="K36" s="17" t="n"/>
+      <c r="D36" s="17" t="n">
+        <v>2947</v>
+      </c>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="17" t="n">
+        <v>2923</v>
+      </c>
+      <c r="G36" s="16" t="n"/>
+      <c r="H36" s="16" t="n"/>
+      <c r="I36" s="17" t="n">
+        <v>1866250</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>453089</v>
+      </c>
+      <c r="K36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -1911,115 +1911,115 @@
       <c r="K37" s="13" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [160ml] / Пенка с содой для глубокого очищения и снятия макияжа</t>
-        </is>
-      </c>
-      <c r="B38" s="14" t="n">
-        <v>307073881</v>
-      </c>
-      <c r="C38" s="15" t="n">
-        <v>64</v>
-      </c>
-      <c r="D38" s="15" t="n">
-        <v>122</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F38" s="15" t="n">
-        <v>64</v>
-      </c>
-      <c r="G38" s="15" t="n">
-        <v>821</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>146</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>52544</v>
-      </c>
-      <c r="J38" s="15" t="n">
-        <v>9344</v>
-      </c>
-      <c r="K38" s="14" t="inlineStr">
-        <is>
-          <t>Рабочий</t>
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="n">
+        <v>151313163</v>
+      </c>
+      <c r="C38" s="19" t="n">
+        <v>7182</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>727</v>
+      </c>
+      <c r="E38" s="19" t="n">
+        <v>785</v>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>727</v>
+      </c>
+      <c r="G38" s="19" t="n">
+        <v>1029</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>211</v>
+      </c>
+      <c r="I38" s="19" t="n">
+        <v>748083</v>
+      </c>
+      <c r="J38" s="19" t="n">
+        <v>153397</v>
+      </c>
+      <c r="K38" s="18" t="inlineStr">
+        <is>
+          <t>★ Драйвер</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="B39" s="14" t="n">
-        <v>151313163</v>
-      </c>
-      <c r="C39" s="15" t="n">
-        <v>7182</v>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>95</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>142</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <v>1029</v>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>211</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>146118</v>
-      </c>
-      <c r="J39" s="15" t="n">
-        <v>29962</v>
+        <v>154160085</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>986</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>1972</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>234</v>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Ограничено остатком</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищающий скраб для лица с содой</t>
+          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [160ml] / Пенка с содой для глубокого очищения и снятия макияжа</t>
         </is>
       </c>
       <c r="B40" s="14" t="n">
-        <v>154160085</v>
-      </c>
-      <c r="C40" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F40" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="15" t="n">
-        <v>986</v>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>117</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>1972</v>
-      </c>
-      <c r="J40" s="15" t="n">
-        <v>234</v>
+        <v>307073881</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>821</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>22988</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>4088</v>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
@@ -2028,31 +2028,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>ИТОГО ETUDEHOUSE</t>
         </is>
       </c>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="18" t="n">
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="17" t="n">
         <v>7248</v>
       </c>
-      <c r="D41" s="18" t="n">
-        <v>236</v>
-      </c>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="18" t="n">
-        <v>208</v>
-      </c>
-      <c r="G41" s="17" t="n"/>
-      <c r="H41" s="17" t="n"/>
-      <c r="I41" s="18" t="n">
-        <v>200634</v>
-      </c>
-      <c r="J41" s="18" t="n">
-        <v>39540</v>
-      </c>
-      <c r="K41" s="17" t="n"/>
+      <c r="D41" s="17" t="n">
+        <v>817</v>
+      </c>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="17" t="n">
+        <v>757</v>
+      </c>
+      <c r="G41" s="16" t="n"/>
+      <c r="H41" s="16" t="n"/>
+      <c r="I41" s="17" t="n">
+        <v>773043</v>
+      </c>
+      <c r="J41" s="17" t="n">
+        <v>157719</v>
+      </c>
+      <c r="K41" s="16" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -2072,310 +2072,310 @@
       <c r="K42" s="13" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
-      <c r="B43" s="19" t="n">
+      <c r="B43" s="18" t="n">
         <v>168956391</v>
       </c>
-      <c r="C43" s="20" t="n">
+      <c r="C43" s="19" t="n">
         <v>6067</v>
       </c>
-      <c r="D43" s="20" t="n">
-        <v>230</v>
+      <c r="D43" s="19" t="n">
+        <v>1807</v>
       </c>
       <c r="E43" s="19" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="F43" s="20" t="n">
-        <v>345</v>
-      </c>
-      <c r="G43" s="20" t="n">
+        <v>1692</v>
+      </c>
+      <c r="F43" s="19" t="n">
+        <v>1807</v>
+      </c>
+      <c r="G43" s="19" t="n">
         <v>1011</v>
       </c>
-      <c r="H43" s="20" t="n">
+      <c r="H43" s="19" t="n">
         <v>208</v>
       </c>
-      <c r="I43" s="20" t="n">
-        <v>348795</v>
-      </c>
-      <c r="J43" s="20" t="n">
-        <v>71760</v>
-      </c>
-      <c r="K43" s="19" t="inlineStr">
-        <is>
-          <t>Затоварка — акцент рекламы</t>
+      <c r="I43" s="19" t="n">
+        <v>1826877</v>
+      </c>
+      <c r="J43" s="19" t="n">
+        <v>375856</v>
+      </c>
+      <c r="K43" s="18" t="inlineStr">
+        <is>
+          <t>★ Драйвер</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="19" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="n">
+        <v>207472742</v>
+      </c>
+      <c r="C44" s="19" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D44" s="19" t="n">
+        <v>1125</v>
+      </c>
+      <c r="E44" s="19" t="n">
+        <v>1069</v>
+      </c>
+      <c r="F44" s="19" t="n">
+        <v>1125</v>
+      </c>
+      <c r="G44" s="19" t="n">
+        <v>1081</v>
+      </c>
+      <c r="H44" s="19" t="n">
+        <v>175</v>
+      </c>
+      <c r="I44" s="19" t="n">
+        <v>1216125</v>
+      </c>
+      <c r="J44" s="19" t="n">
+        <v>196875</v>
+      </c>
+      <c r="K44" s="18" t="inlineStr">
+        <is>
+          <t>★ Драйвер</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
         </is>
       </c>
-      <c r="B44" s="19" t="n">
+      <c r="B45" s="18" t="n">
         <v>169076150</v>
       </c>
-      <c r="C44" s="20" t="n">
+      <c r="C45" s="19" t="n">
         <v>835</v>
       </c>
-      <c r="D44" s="20" t="n">
-        <v>214</v>
-      </c>
-      <c r="E44" s="19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>321</v>
-      </c>
-      <c r="G44" s="20" t="n">
+      <c r="D45" s="19" t="n">
+        <v>474</v>
+      </c>
+      <c r="E45" s="19" t="n">
+        <v>554</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>474</v>
+      </c>
+      <c r="G45" s="19" t="n">
         <v>822</v>
       </c>
-      <c r="H44" s="20" t="n">
+      <c r="H45" s="19" t="n">
         <v>133</v>
       </c>
-      <c r="I44" s="20" t="n">
-        <v>263862</v>
-      </c>
-      <c r="J44" s="20" t="n">
-        <v>42693</v>
-      </c>
-      <c r="K44" s="19" t="inlineStr">
+      <c r="I45" s="19" t="n">
+        <v>389628</v>
+      </c>
+      <c r="J45" s="19" t="n">
+        <v>63042</v>
+      </c>
+      <c r="K45" s="18" t="inlineStr">
         <is>
           <t>★ Драйвер</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
-        </is>
-      </c>
-      <c r="B45" s="14" t="n">
-        <v>207472742</v>
-      </c>
-      <c r="C45" s="15" t="n">
-        <v>3200</v>
-      </c>
-      <c r="D45" s="15" t="n">
-        <v>140</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>210</v>
-      </c>
-      <c r="G45" s="15" t="n">
-        <v>1081</v>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>175</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>227010</v>
-      </c>
-      <c r="J45" s="15" t="n">
-        <v>36750</v>
-      </c>
-      <c r="K45" s="14" t="inlineStr">
-        <is>
-          <t>Затоварка — акцент рекламы</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
-        </is>
-      </c>
-      <c r="B46" s="14" t="n">
-        <v>207476309</v>
-      </c>
-      <c r="C46" s="15" t="n">
-        <v>2298</v>
-      </c>
-      <c r="D46" s="15" t="n">
-        <v>131</v>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>196</v>
-      </c>
-      <c r="G46" s="15" t="n">
-        <v>1029</v>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>172</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>201684</v>
-      </c>
-      <c r="J46" s="15" t="n">
-        <v>33712</v>
-      </c>
-      <c r="K46" s="14" t="inlineStr">
-        <is>
-          <t>Затоварка — акцент рекламы</t>
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="n">
+        <v>207469760</v>
+      </c>
+      <c r="C46" s="19" t="n">
+        <v>852</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>460</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>535</v>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>460</v>
+      </c>
+      <c r="G46" s="19" t="n">
+        <v>1445</v>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>396</v>
+      </c>
+      <c r="I46" s="19" t="n">
+        <v>664700</v>
+      </c>
+      <c r="J46" s="19" t="n">
+        <v>182160</v>
+      </c>
+      <c r="K46" s="18" t="inlineStr">
+        <is>
+          <t>★ Драйвер</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
         </is>
       </c>
       <c r="B47" s="14" t="n">
-        <v>207475898</v>
-      </c>
-      <c r="C47" s="15" t="n">
-        <v>3374</v>
-      </c>
-      <c r="D47" s="15" t="n">
-        <v>107</v>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="F47" s="15" t="n">
-        <v>160</v>
-      </c>
-      <c r="G47" s="15" t="n">
-        <v>1029</v>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>179</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>164640</v>
-      </c>
-      <c r="J47" s="15" t="n">
-        <v>28640</v>
+        <v>419630142</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>821</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>936</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>147888</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>18486</v>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
         </is>
       </c>
       <c r="B48" s="14" t="n">
-        <v>419630142</v>
-      </c>
-      <c r="C48" s="15" t="n">
-        <v>821</v>
-      </c>
-      <c r="D48" s="15" t="n">
-        <v>104</v>
-      </c>
-      <c r="E48" s="14" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="F48" s="15" t="n">
-        <v>156</v>
-      </c>
-      <c r="G48" s="15" t="n">
-        <v>936</v>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>117</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>146016</v>
-      </c>
-      <c r="J48" s="15" t="n">
-        <v>18252</v>
+        <v>207475898</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>3374</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>1029</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>137886</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>23986</v>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
         </is>
       </c>
       <c r="B49" s="14" t="n">
-        <v>207469760</v>
-      </c>
-      <c r="C49" s="15" t="n">
-        <v>852</v>
-      </c>
-      <c r="D49" s="15" t="n">
-        <v>89</v>
-      </c>
-      <c r="E49" s="14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F49" s="15" t="n">
-        <v>134</v>
-      </c>
-      <c r="G49" s="15" t="n">
-        <v>1445</v>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>396</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>193630</v>
-      </c>
-      <c r="J49" s="15" t="n">
-        <v>53064</v>
+        <v>212885914</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>718</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>89032</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>18724</v>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
         </is>
       </c>
       <c r="B50" s="14" t="n">
-        <v>212885914</v>
-      </c>
-      <c r="C50" s="15" t="n">
-        <v>156</v>
-      </c>
-      <c r="D50" s="15" t="n">
-        <v>49</v>
-      </c>
-      <c r="E50" s="14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F50" s="15" t="n">
-        <v>74</v>
-      </c>
-      <c r="G50" s="15" t="n">
-        <v>718</v>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>151</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>53132</v>
-      </c>
-      <c r="J50" s="15" t="n">
-        <v>11174</v>
+        <v>207476309</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>2298</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>421</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>1029</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>87465</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>14620</v>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
@@ -2392,29 +2392,29 @@
       <c r="B51" s="14" t="n">
         <v>207477077</v>
       </c>
-      <c r="C51" s="15" t="n">
+      <c r="C51" s="5" t="n">
         <v>239</v>
       </c>
-      <c r="D51" s="15" t="n">
-        <v>49</v>
-      </c>
-      <c r="E51" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F51" s="15" t="n">
-        <v>74</v>
-      </c>
-      <c r="G51" s="15" t="n">
+      <c r="D51" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>176</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="G51" s="5" t="n">
         <v>1341</v>
       </c>
-      <c r="H51" s="15" t="n">
+      <c r="H51" s="5" t="n">
         <v>271</v>
       </c>
-      <c r="I51" s="15" t="n">
-        <v>99234</v>
-      </c>
-      <c r="J51" s="15" t="n">
-        <v>20054</v>
+      <c r="I51" s="5" t="n">
+        <v>85824</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>17344</v>
       </c>
       <c r="K51" s="14" t="inlineStr">
         <is>
@@ -2431,62 +2431,62 @@
       <c r="B52" s="14" t="n">
         <v>207476777</v>
       </c>
-      <c r="C52" s="15" t="n">
+      <c r="C52" s="5" t="n">
         <v>382</v>
       </c>
-      <c r="D52" s="15" t="n">
+      <c r="D52" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="E52" s="14" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F52" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="G52" s="15" t="n">
+      <c r="E52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="G52" s="5" t="n">
         <v>613</v>
       </c>
-      <c r="H52" s="15" t="n">
+      <c r="H52" s="5" t="n">
         <v>152</v>
       </c>
-      <c r="I52" s="15" t="n">
-        <v>30650</v>
-      </c>
-      <c r="J52" s="15" t="n">
-        <v>7600</v>
+      <c r="I52" s="5" t="n">
+        <v>20229</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>5016</v>
       </c>
       <c r="K52" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>ИТОГО FARMSTAY</t>
         </is>
       </c>
-      <c r="B53" s="17" t="n"/>
-      <c r="C53" s="18" t="n">
+      <c r="B53" s="16" t="n"/>
+      <c r="C53" s="17" t="n">
         <v>18224</v>
       </c>
-      <c r="D53" s="18" t="n">
-        <v>1146</v>
-      </c>
-      <c r="E53" s="17" t="n"/>
-      <c r="F53" s="18" t="n">
-        <v>1720</v>
-      </c>
-      <c r="G53" s="17" t="n"/>
-      <c r="H53" s="17" t="n"/>
-      <c r="I53" s="18" t="n">
-        <v>1728653</v>
-      </c>
-      <c r="J53" s="18" t="n">
-        <v>323699</v>
-      </c>
-      <c r="K53" s="17" t="n"/>
+      <c r="D53" s="17" t="n">
+        <v>4464</v>
+      </c>
+      <c r="E53" s="16" t="n"/>
+      <c r="F53" s="17" t="n">
+        <v>4464</v>
+      </c>
+      <c r="G53" s="16" t="n"/>
+      <c r="H53" s="16" t="n"/>
+      <c r="I53" s="17" t="n">
+        <v>4665654</v>
+      </c>
+      <c r="J53" s="17" t="n">
+        <v>916109</v>
+      </c>
+      <c r="K53" s="16" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -2514,62 +2514,62 @@
       <c r="B55" s="14" t="n">
         <v>207466866</v>
       </c>
-      <c r="C55" s="15" t="n">
+      <c r="C55" s="5" t="n">
         <v>930</v>
       </c>
-      <c r="D55" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="E55" s="14" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="F55" s="15" t="n">
-        <v>84</v>
-      </c>
-      <c r="G55" s="15" t="n">
+      <c r="D55" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G55" s="5" t="n">
         <v>1775</v>
       </c>
-      <c r="H55" s="15" t="n">
+      <c r="H55" s="5" t="n">
         <v>231</v>
       </c>
-      <c r="I55" s="15" t="n">
-        <v>149100</v>
-      </c>
-      <c r="J55" s="15" t="n">
-        <v>19404</v>
+      <c r="I55" s="5" t="n">
+        <v>15975</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>2079</v>
       </c>
       <c r="K55" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="inlineStr">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>ИТОГО HEIMISH</t>
         </is>
       </c>
-      <c r="B56" s="17" t="n"/>
-      <c r="C56" s="18" t="n">
+      <c r="B56" s="16" t="n"/>
+      <c r="C56" s="17" t="n">
         <v>930</v>
       </c>
-      <c r="D56" s="18" t="n">
-        <v>56</v>
-      </c>
-      <c r="E56" s="17" t="n"/>
-      <c r="F56" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="G56" s="17" t="n"/>
-      <c r="H56" s="17" t="n"/>
-      <c r="I56" s="18" t="n">
-        <v>149100</v>
-      </c>
-      <c r="J56" s="18" t="n">
-        <v>19404</v>
-      </c>
-      <c r="K56" s="17" t="n"/>
+      <c r="D56" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G56" s="16" t="n"/>
+      <c r="H56" s="16" t="n"/>
+      <c r="I56" s="17" t="n">
+        <v>15975</v>
+      </c>
+      <c r="J56" s="17" t="n">
+        <v>2079</v>
+      </c>
+      <c r="K56" s="16" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -2589,80 +2589,80 @@
       <c r="K57" s="13" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="19" t="inlineStr">
+      <c r="A58" s="18" t="inlineStr">
         <is>
           <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
-      <c r="B58" s="19" t="n">
+      <c r="B58" s="18" t="n">
         <v>207482718</v>
       </c>
-      <c r="C58" s="20" t="n">
+      <c r="C58" s="19" t="n">
         <v>7139</v>
       </c>
-      <c r="D58" s="20" t="n">
-        <v>276</v>
+      <c r="D58" s="19" t="n">
+        <v>681</v>
       </c>
       <c r="E58" s="19" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="F58" s="20" t="n">
-        <v>414</v>
-      </c>
-      <c r="G58" s="20" t="n">
+        <v>704</v>
+      </c>
+      <c r="F58" s="19" t="n">
+        <v>681</v>
+      </c>
+      <c r="G58" s="19" t="n">
         <v>614</v>
       </c>
-      <c r="H58" s="20" t="n">
+      <c r="H58" s="19" t="n">
         <v>118</v>
       </c>
-      <c r="I58" s="20" t="n">
-        <v>254196</v>
-      </c>
-      <c r="J58" s="20" t="n">
-        <v>48852</v>
-      </c>
-      <c r="K58" s="19" t="inlineStr">
-        <is>
-          <t>Затоварка — акцент рекламы</t>
+      <c r="I58" s="19" t="n">
+        <v>418134</v>
+      </c>
+      <c r="J58" s="19" t="n">
+        <v>80358</v>
+      </c>
+      <c r="K58" s="18" t="inlineStr">
+        <is>
+          <t>★ Драйвер</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="19" t="inlineStr">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
         </is>
       </c>
-      <c r="B59" s="19" t="n">
+      <c r="B59" s="14" t="n">
         <v>207483179</v>
       </c>
-      <c r="C59" s="20" t="n">
+      <c r="C59" s="5" t="n">
         <v>777</v>
       </c>
-      <c r="D59" s="20" t="n">
-        <v>198</v>
-      </c>
-      <c r="E59" s="19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F59" s="20" t="n">
-        <v>297</v>
-      </c>
-      <c r="G59" s="20" t="n">
+      <c r="D59" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="G59" s="5" t="n">
         <v>510</v>
       </c>
-      <c r="H59" s="20" t="n">
+      <c r="H59" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="I59" s="20" t="n">
-        <v>151470</v>
-      </c>
-      <c r="J59" s="20" t="n">
-        <v>21384</v>
-      </c>
-      <c r="K59" s="19" t="inlineStr">
-        <is>
-          <t>★ Драйвер</t>
+      <c r="I59" s="5" t="n">
+        <v>110670</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>15624</v>
+      </c>
+      <c r="K59" s="14" t="inlineStr">
+        <is>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -2675,62 +2675,62 @@
       <c r="B60" s="14" t="n">
         <v>207483780</v>
       </c>
-      <c r="C60" s="15" t="n">
+      <c r="C60" s="5" t="n">
         <v>1598</v>
       </c>
-      <c r="D60" s="15" t="n">
-        <v>54</v>
-      </c>
-      <c r="E60" s="14" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="F60" s="15" t="n">
-        <v>81</v>
-      </c>
-      <c r="G60" s="15" t="n">
+      <c r="D60" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="G60" s="5" t="n">
         <v>613</v>
       </c>
-      <c r="H60" s="15" t="n">
+      <c r="H60" s="5" t="n">
         <v>123</v>
       </c>
-      <c r="I60" s="15" t="n">
-        <v>49653</v>
-      </c>
-      <c r="J60" s="15" t="n">
-        <v>9963</v>
+      <c r="I60" s="5" t="n">
+        <v>93176</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>18696</v>
       </c>
       <c r="K60" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>ИТОГО JIGOTT/JIGOTT-CREAM</t>
         </is>
       </c>
-      <c r="B61" s="17" t="n"/>
-      <c r="C61" s="18" t="n">
+      <c r="B61" s="16" t="n"/>
+      <c r="C61" s="17" t="n">
         <v>9514</v>
       </c>
-      <c r="D61" s="18" t="n">
-        <v>528</v>
-      </c>
-      <c r="E61" s="17" t="n"/>
-      <c r="F61" s="18" t="n">
-        <v>792</v>
-      </c>
-      <c r="G61" s="17" t="n"/>
-      <c r="H61" s="17" t="n"/>
-      <c r="I61" s="18" t="n">
-        <v>455319</v>
-      </c>
-      <c r="J61" s="18" t="n">
-        <v>80199</v>
-      </c>
-      <c r="K61" s="17" t="n"/>
+      <c r="D61" s="17" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E61" s="16" t="n"/>
+      <c r="F61" s="17" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G61" s="16" t="n"/>
+      <c r="H61" s="16" t="n"/>
+      <c r="I61" s="17" t="n">
+        <v>621980</v>
+      </c>
+      <c r="J61" s="17" t="n">
+        <v>114678</v>
+      </c>
+      <c r="K61" s="16" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -2758,62 +2758,62 @@
       <c r="B63" s="14" t="n">
         <v>255574453</v>
       </c>
-      <c r="C63" s="15" t="n">
+      <c r="C63" s="5" t="n">
         <v>1302</v>
       </c>
-      <c r="D63" s="15" t="n">
-        <v>27</v>
-      </c>
-      <c r="E63" s="14" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="F63" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="G63" s="15" t="n">
+      <c r="D63" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="G63" s="5" t="n">
         <v>925</v>
       </c>
-      <c r="H63" s="15" t="n">
+      <c r="H63" s="5" t="n">
         <v>154</v>
       </c>
-      <c r="I63" s="15" t="n">
-        <v>37000</v>
-      </c>
-      <c r="J63" s="15" t="n">
-        <v>6160</v>
+      <c r="I63" s="5" t="n">
+        <v>222000</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>36960</v>
       </c>
       <c r="K63" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+      <c r="A64" s="15" t="inlineStr">
         <is>
           <t>ИТОГО JIGOTT/JIGOTT-MASK</t>
         </is>
       </c>
-      <c r="B64" s="17" t="n"/>
-      <c r="C64" s="18" t="n">
+      <c r="B64" s="16" t="n"/>
+      <c r="C64" s="17" t="n">
         <v>1302</v>
       </c>
-      <c r="D64" s="18" t="n">
-        <v>27</v>
-      </c>
-      <c r="E64" s="17" t="n"/>
-      <c r="F64" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="G64" s="17" t="n"/>
-      <c r="H64" s="17" t="n"/>
-      <c r="I64" s="18" t="n">
-        <v>37000</v>
-      </c>
-      <c r="J64" s="18" t="n">
-        <v>6160</v>
-      </c>
-      <c r="K64" s="17" t="n"/>
+      <c r="D64" s="17" t="n">
+        <v>240</v>
+      </c>
+      <c r="E64" s="16" t="n"/>
+      <c r="F64" s="17" t="n">
+        <v>240</v>
+      </c>
+      <c r="G64" s="16" t="n"/>
+      <c r="H64" s="16" t="n"/>
+      <c r="I64" s="17" t="n">
+        <v>222000</v>
+      </c>
+      <c r="J64" s="17" t="n">
+        <v>36960</v>
+      </c>
+      <c r="K64" s="16" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -2833,80 +2833,80 @@
       <c r="K65" s="13" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
-        </is>
-      </c>
-      <c r="B66" s="14" t="n">
-        <v>212757456</v>
-      </c>
-      <c r="C66" s="15" t="n">
-        <v>1185</v>
-      </c>
-      <c r="D66" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="E66" s="14" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="F66" s="15" t="n">
-        <v>34</v>
-      </c>
-      <c r="G66" s="15" t="n">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="n">
+        <v>212760119</v>
+      </c>
+      <c r="C66" s="19" t="n">
+        <v>1134</v>
+      </c>
+      <c r="D66" s="19" t="n">
+        <v>405</v>
+      </c>
+      <c r="E66" s="19" t="n">
+        <v>96</v>
+      </c>
+      <c r="F66" s="19" t="n">
+        <v>405</v>
+      </c>
+      <c r="G66" s="19" t="n">
         <v>821</v>
       </c>
-      <c r="H66" s="15" t="n">
-        <v>112</v>
-      </c>
-      <c r="I66" s="15" t="n">
-        <v>27914</v>
-      </c>
-      <c r="J66" s="15" t="n">
-        <v>3808</v>
-      </c>
-      <c r="K66" s="14" t="inlineStr">
-        <is>
-          <t>Затоварка — акцент рекламы</t>
+      <c r="H66" s="19" t="n">
+        <v>157</v>
+      </c>
+      <c r="I66" s="19" t="n">
+        <v>332505</v>
+      </c>
+      <c r="J66" s="19" t="n">
+        <v>63585</v>
+      </c>
+      <c r="K66" s="18" t="inlineStr">
+        <is>
+          <t>★ Драйвер</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="B67" s="14" t="n">
-        <v>212760119</v>
-      </c>
-      <c r="C67" s="15" t="n">
-        <v>1134</v>
-      </c>
-      <c r="D67" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="E67" s="14" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="F67" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="G67" s="15" t="n">
+        <v>212757456</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>1185</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="G67" s="5" t="n">
         <v>821</v>
       </c>
-      <c r="H67" s="15" t="n">
-        <v>157</v>
-      </c>
-      <c r="I67" s="15" t="n">
-        <v>22988</v>
-      </c>
-      <c r="J67" s="15" t="n">
-        <v>4396</v>
+      <c r="H67" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>229880</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>31360</v>
       </c>
       <c r="K67" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -2919,33 +2919,33 @@
       <c r="B68" s="14" t="n">
         <v>212759698</v>
       </c>
-      <c r="C68" s="15" t="n">
+      <c r="C68" s="5" t="n">
         <v>202</v>
       </c>
-      <c r="D68" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="E68" s="14" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F68" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="G68" s="15" t="n">
+      <c r="D68" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="G68" s="5" t="n">
         <v>717</v>
       </c>
-      <c r="H68" s="15" t="n">
+      <c r="H68" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="I68" s="15" t="n">
-        <v>12906</v>
-      </c>
-      <c r="J68" s="15" t="n">
-        <v>1692</v>
+      <c r="I68" s="5" t="n">
+        <v>91776</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>12032</v>
       </c>
       <c r="K68" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -2958,62 +2958,62 @@
       <c r="B69" s="14" t="n">
         <v>212883090</v>
       </c>
-      <c r="C69" s="15" t="n">
+      <c r="C69" s="5" t="n">
         <v>222</v>
       </c>
-      <c r="D69" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E69" s="14" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="F69" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="G69" s="15" t="n">
+      <c r="D69" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="G69" s="5" t="n">
         <v>821</v>
       </c>
-      <c r="H69" s="15" t="n">
+      <c r="H69" s="5" t="n">
         <v>165</v>
       </c>
-      <c r="I69" s="15" t="n">
-        <v>12315</v>
-      </c>
-      <c r="J69" s="15" t="n">
-        <v>2475</v>
+      <c r="I69" s="5" t="n">
+        <v>91952</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>18480</v>
       </c>
       <c r="K69" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="inlineStr">
+      <c r="A70" s="15" t="inlineStr">
         <is>
           <t>ИТОГО JIGOTT/JIGOTT-TONER</t>
         </is>
       </c>
-      <c r="B70" s="17" t="n"/>
-      <c r="C70" s="18" t="n">
+      <c r="B70" s="16" t="n"/>
+      <c r="C70" s="17" t="n">
         <v>2743</v>
       </c>
-      <c r="D70" s="18" t="n">
-        <v>64</v>
-      </c>
-      <c r="E70" s="17" t="n"/>
-      <c r="F70" s="18" t="n">
-        <v>95</v>
-      </c>
-      <c r="G70" s="17" t="n"/>
-      <c r="H70" s="17" t="n"/>
-      <c r="I70" s="18" t="n">
-        <v>76123</v>
-      </c>
-      <c r="J70" s="18" t="n">
-        <v>12371</v>
-      </c>
-      <c r="K70" s="17" t="n"/>
+      <c r="D70" s="17" t="n">
+        <v>925</v>
+      </c>
+      <c r="E70" s="16" t="n"/>
+      <c r="F70" s="17" t="n">
+        <v>925</v>
+      </c>
+      <c r="G70" s="16" t="n"/>
+      <c r="H70" s="16" t="n"/>
+      <c r="I70" s="17" t="n">
+        <v>746113</v>
+      </c>
+      <c r="J70" s="17" t="n">
+        <v>125457</v>
+      </c>
+      <c r="K70" s="16" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -3041,62 +3041,62 @@
       <c r="B72" s="14" t="n">
         <v>214977901</v>
       </c>
-      <c r="C72" s="15" t="n">
+      <c r="C72" s="5" t="n">
         <v>980</v>
       </c>
-      <c r="D72" s="15" t="n">
-        <v>49</v>
-      </c>
-      <c r="E72" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="F72" s="15" t="n">
-        <v>74</v>
-      </c>
-      <c r="G72" s="15" t="n">
+      <c r="D72" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="G72" s="5" t="n">
         <v>1133</v>
       </c>
-      <c r="H72" s="15" t="n">
+      <c r="H72" s="5" t="n">
         <v>175</v>
       </c>
-      <c r="I72" s="15" t="n">
-        <v>83842</v>
-      </c>
-      <c r="J72" s="15" t="n">
-        <v>12950</v>
+      <c r="I72" s="5" t="n">
+        <v>185812</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>28700</v>
       </c>
       <c r="K72" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="inlineStr">
+      <c r="A73" s="15" t="inlineStr">
         <is>
           <t>ИТОГО JMSOLUTION/JM-MASKPACKBLACK</t>
         </is>
       </c>
-      <c r="B73" s="17" t="n"/>
-      <c r="C73" s="18" t="n">
+      <c r="B73" s="16" t="n"/>
+      <c r="C73" s="17" t="n">
         <v>980</v>
       </c>
-      <c r="D73" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="E73" s="17" t="n"/>
-      <c r="F73" s="18" t="n">
-        <v>74</v>
-      </c>
-      <c r="G73" s="17" t="n"/>
-      <c r="H73" s="17" t="n"/>
-      <c r="I73" s="18" t="n">
-        <v>83842</v>
-      </c>
-      <c r="J73" s="18" t="n">
-        <v>12950</v>
-      </c>
-      <c r="K73" s="17" t="n"/>
+      <c r="D73" s="17" t="n">
+        <v>164</v>
+      </c>
+      <c r="E73" s="16" t="n"/>
+      <c r="F73" s="17" t="n">
+        <v>164</v>
+      </c>
+      <c r="G73" s="16" t="n"/>
+      <c r="H73" s="16" t="n"/>
+      <c r="I73" s="17" t="n">
+        <v>185812</v>
+      </c>
+      <c r="J73" s="17" t="n">
+        <v>28700</v>
+      </c>
+      <c r="K73" s="16" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -3124,62 +3124,62 @@
       <c r="B75" s="14" t="n">
         <v>214964091</v>
       </c>
-      <c r="C75" s="15" t="n">
+      <c r="C75" s="5" t="n">
         <v>832</v>
       </c>
-      <c r="D75" s="15" t="n">
-        <v>52</v>
-      </c>
-      <c r="E75" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="F75" s="15" t="n">
-        <v>78</v>
-      </c>
-      <c r="G75" s="15" t="n">
+      <c r="D75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="G75" s="5" t="n">
         <v>1341</v>
       </c>
-      <c r="H75" s="15" t="n">
+      <c r="H75" s="5" t="n">
         <v>318</v>
       </c>
-      <c r="I75" s="15" t="n">
-        <v>104598</v>
-      </c>
-      <c r="J75" s="15" t="n">
-        <v>24804</v>
+      <c r="I75" s="5" t="n">
+        <v>266859</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>63282</v>
       </c>
       <c r="K75" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="inlineStr">
+      <c r="A76" s="15" t="inlineStr">
         <is>
           <t>ИТОГО JMSOLUTION/JM-MASKPACKDISNEY</t>
         </is>
       </c>
-      <c r="B76" s="17" t="n"/>
-      <c r="C76" s="18" t="n">
+      <c r="B76" s="16" t="n"/>
+      <c r="C76" s="17" t="n">
         <v>832</v>
       </c>
-      <c r="D76" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="E76" s="17" t="n"/>
-      <c r="F76" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="G76" s="17" t="n"/>
-      <c r="H76" s="17" t="n"/>
-      <c r="I76" s="18" t="n">
-        <v>104598</v>
-      </c>
-      <c r="J76" s="18" t="n">
-        <v>24804</v>
-      </c>
-      <c r="K76" s="17" t="n"/>
+      <c r="D76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="16" t="n"/>
+      <c r="F76" s="17" t="n">
+        <v>199</v>
+      </c>
+      <c r="G76" s="16" t="n"/>
+      <c r="H76" s="16" t="n"/>
+      <c r="I76" s="17" t="n">
+        <v>266859</v>
+      </c>
+      <c r="J76" s="17" t="n">
+        <v>63282</v>
+      </c>
+      <c r="K76" s="16" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -3207,62 +3207,62 @@
       <c r="B78" s="14" t="n">
         <v>210575566</v>
       </c>
-      <c r="C78" s="15" t="n">
+      <c r="C78" s="5" t="n">
         <v>353</v>
       </c>
-      <c r="D78" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E78" s="14" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="F78" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G78" s="15" t="n">
+      <c r="D78" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G78" s="5" t="n">
         <v>510</v>
       </c>
-      <c r="H78" s="15" t="n">
+      <c r="H78" s="5" t="n">
         <v>155</v>
       </c>
-      <c r="I78" s="15" t="n">
-        <v>5100</v>
-      </c>
-      <c r="J78" s="15" t="n">
-        <v>1550</v>
+      <c r="I78" s="5" t="n">
+        <v>7650</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>2325</v>
       </c>
       <c r="K78" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+      <c r="A79" s="15" t="inlineStr">
         <is>
           <t>ИТОГО LEBELAGE</t>
         </is>
       </c>
-      <c r="B79" s="17" t="n"/>
-      <c r="C79" s="18" t="n">
+      <c r="B79" s="16" t="n"/>
+      <c r="C79" s="17" t="n">
         <v>353</v>
       </c>
-      <c r="D79" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="E79" s="17" t="n"/>
-      <c r="F79" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G79" s="17" t="n"/>
-      <c r="H79" s="17" t="n"/>
-      <c r="I79" s="18" t="n">
-        <v>5100</v>
-      </c>
-      <c r="J79" s="18" t="n">
-        <v>1550</v>
-      </c>
-      <c r="K79" s="17" t="n"/>
+      <c r="D79" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E79" s="16" t="n"/>
+      <c r="F79" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="G79" s="16" t="n"/>
+      <c r="H79" s="16" t="n"/>
+      <c r="I79" s="17" t="n">
+        <v>7650</v>
+      </c>
+      <c r="J79" s="17" t="n">
+        <v>2325</v>
+      </c>
+      <c r="K79" s="16" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -3290,29 +3290,29 @@
       <c r="B81" s="14" t="n">
         <v>868761530</v>
       </c>
-      <c r="C81" s="15" t="n">
+      <c r="C81" s="5" t="n">
         <v>226</v>
       </c>
-      <c r="D81" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="E81" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F81" s="15" t="n">
-        <v>84</v>
-      </c>
-      <c r="G81" s="15" t="n">
+      <c r="D81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="G81" s="5" t="n">
         <v>509</v>
       </c>
-      <c r="H81" s="15" t="n">
+      <c r="H81" s="5" t="n">
         <v>139</v>
       </c>
-      <c r="I81" s="15" t="n">
-        <v>42756</v>
-      </c>
-      <c r="J81" s="15" t="n">
-        <v>11676</v>
+      <c r="I81" s="5" t="n">
+        <v>71769</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>19599</v>
       </c>
       <c r="K81" s="14" t="inlineStr">
         <is>
@@ -3321,31 +3321,31 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="inlineStr">
+      <c r="A82" s="15" t="inlineStr">
         <is>
           <t>ИТОГО LANEIGE</t>
         </is>
       </c>
-      <c r="B82" s="17" t="n"/>
-      <c r="C82" s="18" t="n">
+      <c r="B82" s="16" t="n"/>
+      <c r="C82" s="17" t="n">
         <v>226</v>
       </c>
-      <c r="D82" s="18" t="n">
-        <v>56</v>
-      </c>
-      <c r="E82" s="17" t="n"/>
-      <c r="F82" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="G82" s="17" t="n"/>
-      <c r="H82" s="17" t="n"/>
-      <c r="I82" s="18" t="n">
-        <v>42756</v>
-      </c>
-      <c r="J82" s="18" t="n">
-        <v>11676</v>
-      </c>
-      <c r="K82" s="17" t="n"/>
+      <c r="D82" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="16" t="n"/>
+      <c r="F82" s="17" t="n">
+        <v>141</v>
+      </c>
+      <c r="G82" s="16" t="n"/>
+      <c r="H82" s="16" t="n"/>
+      <c r="I82" s="17" t="n">
+        <v>71769</v>
+      </c>
+      <c r="J82" s="17" t="n">
+        <v>19599</v>
+      </c>
+      <c r="K82" s="16" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
@@ -3367,35 +3367,35 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
       <c r="B84" s="14" t="n">
-        <v>198143251</v>
-      </c>
-      <c r="C84" s="15" t="n">
-        <v>490</v>
-      </c>
-      <c r="D84" s="15" t="n">
-        <v>92</v>
-      </c>
-      <c r="E84" s="14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F84" s="15" t="n">
-        <v>138</v>
-      </c>
-      <c r="G84" s="15" t="n">
-        <v>1667</v>
-      </c>
-      <c r="H84" s="15" t="n">
-        <v>221</v>
-      </c>
-      <c r="I84" s="15" t="n">
-        <v>230046</v>
-      </c>
-      <c r="J84" s="15" t="n">
-        <v>30498</v>
+        <v>198147185</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>1246</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>2795</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>759</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>575770</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>156354</v>
       </c>
       <c r="K84" s="14" t="inlineStr">
         <is>
@@ -3412,72 +3412,72 @@
       <c r="B85" s="14" t="n">
         <v>198156472</v>
       </c>
-      <c r="C85" s="15" t="n">
+      <c r="C85" s="5" t="n">
         <v>639</v>
       </c>
-      <c r="D85" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="E85" s="14" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F85" s="15" t="n">
-        <v>84</v>
-      </c>
-      <c r="G85" s="15" t="n">
+      <c r="D85" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="G85" s="5" t="n">
         <v>1860</v>
       </c>
-      <c r="H85" s="15" t="n">
+      <c r="H85" s="5" t="n">
         <v>444</v>
       </c>
-      <c r="I85" s="15" t="n">
-        <v>156240</v>
-      </c>
-      <c r="J85" s="15" t="n">
-        <v>37296</v>
+      <c r="I85" s="5" t="n">
+        <v>332940</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>79476</v>
       </c>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
         </is>
       </c>
       <c r="B86" s="14" t="n">
-        <v>198147185</v>
-      </c>
-      <c r="C86" s="15" t="n">
-        <v>1246</v>
-      </c>
-      <c r="D86" s="15" t="n">
-        <v>39</v>
-      </c>
-      <c r="E86" s="14" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="F86" s="15" t="n">
-        <v>58</v>
-      </c>
-      <c r="G86" s="15" t="n">
-        <v>2795</v>
-      </c>
-      <c r="H86" s="15" t="n">
-        <v>759</v>
-      </c>
-      <c r="I86" s="15" t="n">
-        <v>162110</v>
-      </c>
-      <c r="J86" s="15" t="n">
-        <v>44022</v>
+        <v>198143251</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>490</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>1667</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>221</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>103354</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>13702</v>
       </c>
       <c r="K86" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -3490,33 +3490,33 @@
       <c r="B87" s="14" t="n">
         <v>868575374</v>
       </c>
-      <c r="C87" s="15" t="n">
+      <c r="C87" s="5" t="n">
         <v>477</v>
       </c>
-      <c r="D87" s="15" t="n">
-        <v>33</v>
-      </c>
-      <c r="E87" s="14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F87" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="G87" s="15" t="n">
+      <c r="D87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="G87" s="5" t="n">
         <v>2276</v>
       </c>
-      <c r="H87" s="15" t="n">
+      <c r="H87" s="5" t="n">
         <v>542</v>
       </c>
-      <c r="I87" s="15" t="n">
-        <v>113800</v>
-      </c>
-      <c r="J87" s="15" t="n">
-        <v>27100</v>
+      <c r="I87" s="5" t="n">
+        <v>141112</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>33604</v>
       </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -3529,29 +3529,29 @@
       <c r="B88" s="14" t="n">
         <v>198156698</v>
       </c>
-      <c r="C88" s="15" t="n">
+      <c r="C88" s="5" t="n">
         <v>151</v>
       </c>
-      <c r="D88" s="15" t="n">
-        <v>27</v>
-      </c>
-      <c r="E88" s="14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F88" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="G88" s="15" t="n">
+      <c r="D88" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G88" s="5" t="n">
         <v>2483</v>
       </c>
-      <c r="H88" s="15" t="n">
+      <c r="H88" s="5" t="n">
         <v>606</v>
       </c>
-      <c r="I88" s="15" t="n">
-        <v>99320</v>
-      </c>
-      <c r="J88" s="15" t="n">
-        <v>24240</v>
+      <c r="I88" s="5" t="n">
+        <v>124150</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>30300</v>
       </c>
       <c r="K88" s="14" t="inlineStr">
         <is>
@@ -3568,62 +3568,62 @@
       <c r="B89" s="14" t="n">
         <v>868700077</v>
       </c>
-      <c r="C89" s="15" t="n">
+      <c r="C89" s="5" t="n">
         <v>603</v>
       </c>
-      <c r="D89" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E89" s="14" t="n">
-        <v>301.5</v>
-      </c>
-      <c r="F89" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G89" s="15" t="n">
+      <c r="D89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="G89" s="5" t="n">
         <v>3004</v>
       </c>
-      <c r="H89" s="15" t="n">
+      <c r="H89" s="5" t="n">
         <v>690</v>
       </c>
-      <c r="I89" s="15" t="n">
-        <v>9012</v>
-      </c>
-      <c r="J89" s="15" t="n">
-        <v>2070</v>
+      <c r="I89" s="5" t="n">
+        <v>123164</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>28290</v>
       </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="inlineStr">
+      <c r="A90" s="15" t="inlineStr">
         <is>
           <t>ИТОГО MANYO</t>
         </is>
       </c>
-      <c r="B90" s="17" t="n"/>
-      <c r="C90" s="18" t="n">
+      <c r="B90" s="16" t="n"/>
+      <c r="C90" s="17" t="n">
         <v>3606</v>
       </c>
-      <c r="D90" s="18" t="n">
-        <v>249</v>
-      </c>
-      <c r="E90" s="17" t="n"/>
-      <c r="F90" s="18" t="n">
-        <v>373</v>
-      </c>
-      <c r="G90" s="17" t="n"/>
-      <c r="H90" s="17" t="n"/>
-      <c r="I90" s="18" t="n">
-        <v>770528</v>
-      </c>
-      <c r="J90" s="18" t="n">
-        <v>165226</v>
-      </c>
-      <c r="K90" s="17" t="n"/>
+      <c r="D90" s="17" t="n">
+        <v>497</v>
+      </c>
+      <c r="E90" s="16" t="n"/>
+      <c r="F90" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="G90" s="16" t="n"/>
+      <c r="H90" s="16" t="n"/>
+      <c r="I90" s="17" t="n">
+        <v>1400490</v>
+      </c>
+      <c r="J90" s="17" t="n">
+        <v>341726</v>
+      </c>
+      <c r="K90" s="16" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
@@ -3651,62 +3651,62 @@
       <c r="B92" s="14" t="n">
         <v>183030830</v>
       </c>
-      <c r="C92" s="15" t="n">
+      <c r="C92" s="5" t="n">
         <v>105</v>
       </c>
-      <c r="D92" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E92" s="14" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F92" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="G92" s="15" t="n">
+      <c r="D92" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G92" s="5" t="n">
         <v>1609</v>
       </c>
-      <c r="H92" s="15" t="n">
+      <c r="H92" s="5" t="n">
         <v>201</v>
       </c>
-      <c r="I92" s="15" t="n">
-        <v>19308</v>
-      </c>
-      <c r="J92" s="15" t="n">
-        <v>2412</v>
+      <c r="I92" s="5" t="n">
+        <v>40225</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>5025</v>
       </c>
       <c r="K92" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="inlineStr">
+      <c r="A93" s="15" t="inlineStr">
         <is>
           <t>ИТОГО MASIL</t>
         </is>
       </c>
-      <c r="B93" s="17" t="n"/>
-      <c r="C93" s="18" t="n">
+      <c r="B93" s="16" t="n"/>
+      <c r="C93" s="17" t="n">
         <v>105</v>
       </c>
-      <c r="D93" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="E93" s="17" t="n"/>
-      <c r="F93" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="G93" s="17" t="n"/>
-      <c r="H93" s="17" t="n"/>
-      <c r="I93" s="18" t="n">
-        <v>19308</v>
-      </c>
-      <c r="J93" s="18" t="n">
-        <v>2412</v>
-      </c>
-      <c r="K93" s="17" t="n"/>
+      <c r="D93" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E93" s="16" t="n"/>
+      <c r="F93" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="G93" s="16" t="n"/>
+      <c r="H93" s="16" t="n"/>
+      <c r="I93" s="17" t="n">
+        <v>40225</v>
+      </c>
+      <c r="J93" s="17" t="n">
+        <v>5025</v>
+      </c>
+      <c r="K93" s="16" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
@@ -3726,80 +3726,80 @@
       <c r="K94" s="13" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="19" t="inlineStr">
+      <c r="A95" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
         </is>
       </c>
-      <c r="B95" s="19" t="n">
+      <c r="B95" s="14" t="n">
         <v>179611207</v>
       </c>
-      <c r="C95" s="20" t="n">
+      <c r="C95" s="5" t="n">
         <v>608</v>
       </c>
-      <c r="D95" s="20" t="n">
-        <v>220</v>
-      </c>
-      <c r="E95" s="19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F95" s="20" t="n">
-        <v>330</v>
-      </c>
-      <c r="G95" s="20" t="n">
+      <c r="D95" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="G95" s="5" t="n">
         <v>991</v>
       </c>
-      <c r="H95" s="20" t="n">
+      <c r="H95" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="I95" s="20" t="n">
-        <v>327030</v>
-      </c>
-      <c r="J95" s="20" t="n">
-        <v>41250</v>
-      </c>
-      <c r="K95" s="19" t="inlineStr">
-        <is>
-          <t>★ Драйвер</t>
+      <c r="I95" s="5" t="n">
+        <v>41622</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>5250</v>
+      </c>
+      <c r="K95" s="14" t="inlineStr">
+        <is>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="19" t="inlineStr">
+      <c r="A96" s="14" t="inlineStr">
         <is>
           <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
         </is>
       </c>
-      <c r="B96" s="19" t="n">
+      <c r="B96" s="14" t="n">
         <v>151175880</v>
       </c>
-      <c r="C96" s="20" t="n">
+      <c r="C96" s="5" t="n">
         <v>549</v>
       </c>
-      <c r="D96" s="20" t="n">
-        <v>160</v>
-      </c>
-      <c r="E96" s="19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F96" s="20" t="n">
-        <v>240</v>
-      </c>
-      <c r="G96" s="20" t="n">
+      <c r="D96" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="G96" s="5" t="n">
         <v>939</v>
       </c>
-      <c r="H96" s="20" t="n">
+      <c r="H96" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="I96" s="20" t="n">
-        <v>225360</v>
-      </c>
-      <c r="J96" s="20" t="n">
-        <v>27840</v>
-      </c>
-      <c r="K96" s="19" t="inlineStr">
-        <is>
-          <t>★ Драйвер</t>
+      <c r="I96" s="5" t="n">
+        <v>36621</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>4524</v>
+      </c>
+      <c r="K96" s="14" t="inlineStr">
+        <is>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -3812,29 +3812,29 @@
       <c r="B97" s="14" t="n">
         <v>151175877</v>
       </c>
-      <c r="C97" s="15" t="n">
+      <c r="C97" s="5" t="n">
         <v>501</v>
       </c>
-      <c r="D97" s="15" t="n">
-        <v>137</v>
-      </c>
-      <c r="E97" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F97" s="15" t="n">
-        <v>206</v>
-      </c>
-      <c r="G97" s="15" t="n">
+      <c r="D97" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G97" s="5" t="n">
         <v>993</v>
       </c>
-      <c r="H97" s="15" t="n">
+      <c r="H97" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="I97" s="15" t="n">
-        <v>204558</v>
-      </c>
-      <c r="J97" s="15" t="n">
-        <v>25750</v>
+      <c r="I97" s="5" t="n">
+        <v>34755</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>4375</v>
       </c>
       <c r="K97" s="14" t="inlineStr">
         <is>
@@ -3845,35 +3845,35 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
         </is>
       </c>
       <c r="B98" s="14" t="n">
-        <v>179611278</v>
-      </c>
-      <c r="C98" s="15" t="n">
-        <v>156</v>
-      </c>
-      <c r="D98" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="E98" s="14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F98" s="15" t="n">
-        <v>84</v>
-      </c>
-      <c r="G98" s="15" t="n">
-        <v>990</v>
-      </c>
-      <c r="H98" s="15" t="n">
-        <v>125</v>
-      </c>
-      <c r="I98" s="15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="J98" s="15" t="n">
-        <v>10500</v>
+        <v>180711104</v>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>405</v>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>1029</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>33957</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>4983</v>
       </c>
       <c r="K98" s="14" t="inlineStr">
         <is>
@@ -3884,156 +3884,156 @@
     <row r="99">
       <c r="A99" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="B99" s="14" t="n">
-        <v>180988755</v>
-      </c>
-      <c r="C99" s="15" t="n">
-        <v>406</v>
-      </c>
-      <c r="D99" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="E99" s="14" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="F99" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="G99" s="15" t="n">
-        <v>1164</v>
-      </c>
-      <c r="H99" s="15" t="n">
-        <v>146</v>
-      </c>
-      <c r="I99" s="15" t="n">
-        <v>69840</v>
-      </c>
-      <c r="J99" s="15" t="n">
-        <v>8760</v>
+        <v>180992464</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>1394</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>39032</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>4956</v>
       </c>
       <c r="K99" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
         </is>
       </c>
       <c r="B100" s="14" t="n">
-        <v>180711104</v>
-      </c>
-      <c r="C100" s="15" t="n">
-        <v>405</v>
-      </c>
-      <c r="D100" s="15" t="n">
-        <v>36</v>
-      </c>
-      <c r="E100" s="14" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F100" s="15" t="n">
-        <v>54</v>
-      </c>
-      <c r="G100" s="15" t="n">
+        <v>179611304</v>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G100" s="5" t="n">
         <v>1029</v>
       </c>
-      <c r="H100" s="15" t="n">
-        <v>151</v>
-      </c>
-      <c r="I100" s="15" t="n">
-        <v>55566</v>
-      </c>
-      <c r="J100" s="15" t="n">
-        <v>8154</v>
+      <c r="H100" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>28812</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>3780</v>
       </c>
       <c r="K100" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
+          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
       <c r="B101" s="14" t="n">
-        <v>179611231</v>
-      </c>
-      <c r="C101" s="15" t="n">
-        <v>641</v>
-      </c>
-      <c r="D101" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="E101" s="14" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="F101" s="15" t="n">
-        <v>38</v>
-      </c>
-      <c r="G101" s="15" t="n">
-        <v>1029</v>
-      </c>
-      <c r="H101" s="15" t="n">
-        <v>178</v>
-      </c>
-      <c r="I101" s="15" t="n">
-        <v>39102</v>
-      </c>
-      <c r="J101" s="15" t="n">
-        <v>6764</v>
+        <v>180988755</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>406</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>1164</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>17460</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>2190</v>
       </c>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
+          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
         </is>
       </c>
       <c r="B102" s="14" t="n">
-        <v>179611304</v>
-      </c>
-      <c r="C102" s="15" t="n">
-        <v>144</v>
-      </c>
-      <c r="D102" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="E102" s="14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="F102" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="G102" s="15" t="n">
+        <v>179611231</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>641</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G102" s="5" t="n">
         <v>1029</v>
       </c>
-      <c r="H102" s="15" t="n">
-        <v>135</v>
-      </c>
-      <c r="I102" s="15" t="n">
-        <v>28812</v>
-      </c>
-      <c r="J102" s="15" t="n">
-        <v>3780</v>
+      <c r="H102" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>11319</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>1958</v>
       </c>
       <c r="K102" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -4046,171 +4046,175 @@
       <c r="B103" s="14" t="n">
         <v>180987509</v>
       </c>
-      <c r="C103" s="15" t="n">
+      <c r="C103" s="5" t="n">
         <v>202</v>
       </c>
-      <c r="D103" s="15" t="n">
+      <c r="D103" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="E103" s="14" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F103" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="G103" s="15" t="n">
+      <c r="F103" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G103" s="5" t="n">
         <v>1146</v>
       </c>
-      <c r="H103" s="15" t="n">
+      <c r="H103" s="5" t="n">
         <v>146</v>
       </c>
-      <c r="I103" s="15" t="n">
-        <v>32088</v>
-      </c>
-      <c r="J103" s="15" t="n">
-        <v>4088</v>
+      <c r="I103" s="5" t="n">
+        <v>11460</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>1460</v>
       </c>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
         </is>
       </c>
       <c r="B104" s="14" t="n">
-        <v>180992464</v>
-      </c>
-      <c r="C104" s="15" t="n">
-        <v>89</v>
-      </c>
-      <c r="D104" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E104" s="14" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="F104" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="G104" s="15" t="n">
-        <v>1394</v>
-      </c>
-      <c r="H104" s="15" t="n">
-        <v>177</v>
-      </c>
-      <c r="I104" s="15" t="n">
-        <v>20910</v>
-      </c>
-      <c r="J104" s="15" t="n">
-        <v>2655</v>
+        <v>179611278</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>990</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>6930</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>875</v>
       </c>
       <c r="K104" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="21" t="inlineStr">
+      <c r="A105" s="20" t="inlineStr">
         <is>
           <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
         </is>
       </c>
-      <c r="B105" s="21" t="inlineStr"/>
-      <c r="C105" s="22" t="n">
+      <c r="B105" s="20" t="inlineStr"/>
+      <c r="C105" s="21" t="n">
         <v>320</v>
       </c>
-      <c r="D105" s="22" t="n">
+      <c r="D105" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E105" s="21" t="n"/>
-      <c r="F105" s="22" t="n">
+      <c r="E105" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G105" s="22" t="n">
+      <c r="F105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="21" t="n">
         <v>262</v>
       </c>
-      <c r="H105" s="22" t="n">
+      <c r="H105" s="21" t="n">
         <v>21</v>
       </c>
-      <c r="I105" s="22" t="n">
+      <c r="I105" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="J105" s="22" t="n">
+      <c r="J105" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="K105" s="21" t="inlineStr">
-        <is>
-          <t>Нет продаж — разогнать/распродать</t>
+      <c r="K105" s="20" t="inlineStr">
+        <is>
+          <t>Нет истории — разогнать/распродать</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="21" t="inlineStr">
+      <c r="A106" s="20" t="inlineStr">
         <is>
           <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
         </is>
       </c>
-      <c r="B106" s="21" t="inlineStr"/>
-      <c r="C106" s="22" t="n">
+      <c r="B106" s="20" t="inlineStr"/>
+      <c r="C106" s="21" t="n">
         <v>428</v>
       </c>
-      <c r="D106" s="22" t="n">
+      <c r="D106" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E106" s="21" t="n"/>
-      <c r="F106" s="22" t="n">
+      <c r="E106" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G106" s="22" t="n">
+      <c r="F106" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="21" t="n">
         <v>262</v>
       </c>
-      <c r="H106" s="22" t="n">
+      <c r="H106" s="21" t="n">
         <v>21</v>
       </c>
-      <c r="I106" s="22" t="n">
+      <c r="I106" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="J106" s="22" t="n">
+      <c r="J106" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="K106" s="21" t="inlineStr">
-        <is>
-          <t>Нет продаж — разогнать/распродать</t>
+      <c r="K106" s="20" t="inlineStr">
+        <is>
+          <t>Нет истории — разогнать/распродать</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="16" t="inlineStr">
+      <c r="A107" s="15" t="inlineStr">
         <is>
           <t>ИТОГО PETITFEE/PETITFEE-EYEPATCH</t>
         </is>
       </c>
-      <c r="B107" s="17" t="n"/>
-      <c r="C107" s="18" t="n">
+      <c r="B107" s="16" t="n"/>
+      <c r="C107" s="17" t="n">
         <v>4449</v>
       </c>
-      <c r="D107" s="18" t="n">
-        <v>722</v>
-      </c>
-      <c r="E107" s="17" t="n"/>
-      <c r="F107" s="18" t="n">
-        <v>1083</v>
-      </c>
-      <c r="G107" s="17" t="n"/>
-      <c r="H107" s="17" t="n"/>
-      <c r="I107" s="18" t="n">
-        <v>1086426</v>
-      </c>
-      <c r="J107" s="18" t="n">
-        <v>139541</v>
-      </c>
-      <c r="K107" s="17" t="n"/>
+      <c r="D107" s="17" t="n">
+        <v>248</v>
+      </c>
+      <c r="E107" s="16" t="n"/>
+      <c r="F107" s="17" t="n">
+        <v>248</v>
+      </c>
+      <c r="G107" s="16" t="n"/>
+      <c r="H107" s="16" t="n"/>
+      <c r="I107" s="17" t="n">
+        <v>261968</v>
+      </c>
+      <c r="J107" s="17" t="n">
+        <v>34351</v>
+      </c>
+      <c r="K107" s="16" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
@@ -4238,29 +4242,29 @@
       <c r="B109" s="14" t="n">
         <v>226115324</v>
       </c>
-      <c r="C109" s="15" t="n">
+      <c r="C109" s="5" t="n">
         <v>741</v>
       </c>
-      <c r="D109" s="15" t="n">
-        <v>125</v>
-      </c>
-      <c r="E109" s="14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F109" s="15" t="n">
-        <v>188</v>
-      </c>
-      <c r="G109" s="15" t="n">
+      <c r="D109" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="G109" s="5" t="n">
         <v>1193</v>
       </c>
-      <c r="H109" s="15" t="n">
+      <c r="H109" s="5" t="n">
         <v>146</v>
       </c>
-      <c r="I109" s="15" t="n">
-        <v>224284</v>
-      </c>
-      <c r="J109" s="15" t="n">
-        <v>27448</v>
+      <c r="I109" s="5" t="n">
+        <v>62036</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>7592</v>
       </c>
       <c r="K109" s="14" t="inlineStr">
         <is>
@@ -4271,35 +4275,35 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
         </is>
       </c>
       <c r="B110" s="14" t="n">
-        <v>226115248</v>
-      </c>
-      <c r="C110" s="15" t="n">
-        <v>399</v>
-      </c>
-      <c r="D110" s="15" t="n">
-        <v>81</v>
-      </c>
-      <c r="E110" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F110" s="15" t="n">
-        <v>122</v>
-      </c>
-      <c r="G110" s="15" t="n">
-        <v>1159</v>
-      </c>
-      <c r="H110" s="15" t="n">
-        <v>149</v>
-      </c>
-      <c r="I110" s="15" t="n">
-        <v>141398</v>
-      </c>
-      <c r="J110" s="15" t="n">
-        <v>18178</v>
+        <v>226114831</v>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>327</v>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>1341</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>243</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>53640</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>9720</v>
       </c>
       <c r="K110" s="14" t="inlineStr">
         <is>
@@ -4310,35 +4314,35 @@
     <row r="111">
       <c r="A111" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
         </is>
       </c>
       <c r="B111" s="14" t="n">
-        <v>226115478</v>
-      </c>
-      <c r="C111" s="15" t="n">
-        <v>292</v>
-      </c>
-      <c r="D111" s="15" t="n">
-        <v>79</v>
-      </c>
-      <c r="E111" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F111" s="15" t="n">
-        <v>118</v>
-      </c>
-      <c r="G111" s="15" t="n">
-        <v>1130</v>
-      </c>
-      <c r="H111" s="15" t="n">
-        <v>143</v>
-      </c>
-      <c r="I111" s="15" t="n">
-        <v>133340</v>
-      </c>
-      <c r="J111" s="15" t="n">
-        <v>16874</v>
+        <v>226114935</v>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>529</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>46878</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>5928</v>
       </c>
       <c r="K111" s="14" t="inlineStr">
         <is>
@@ -4349,74 +4353,74 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
         </is>
       </c>
       <c r="B112" s="14" t="n">
-        <v>226114935</v>
-      </c>
-      <c r="C112" s="15" t="n">
-        <v>529</v>
-      </c>
-      <c r="D112" s="15" t="n">
-        <v>57</v>
-      </c>
-      <c r="E112" s="14" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="F112" s="15" t="n">
-        <v>86</v>
-      </c>
-      <c r="G112" s="15" t="n">
-        <v>1202</v>
-      </c>
-      <c r="H112" s="15" t="n">
-        <v>152</v>
-      </c>
-      <c r="I112" s="15" t="n">
-        <v>103372</v>
-      </c>
-      <c r="J112" s="15" t="n">
-        <v>13072</v>
+        <v>226115248</v>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>399</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>1159</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>31293</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>4023</v>
       </c>
       <c r="K112" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - MASK 6 (блек, агава, какао, артишок, голд, ромашка)</t>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
         </is>
       </c>
       <c r="B113" s="14" t="n">
-        <v>1175175447</v>
-      </c>
-      <c r="C113" s="15" t="n">
-        <v>106</v>
-      </c>
-      <c r="D113" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="E113" s="14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F113" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="G113" s="15" t="n">
-        <v>1376</v>
-      </c>
-      <c r="H113" s="15" t="n">
-        <v>178</v>
-      </c>
-      <c r="I113" s="15" t="n">
-        <v>82560</v>
-      </c>
-      <c r="J113" s="15" t="n">
-        <v>10680</v>
+        <v>226115141</v>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>1148</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>29848</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>3718</v>
       </c>
       <c r="K113" s="14" t="inlineStr">
         <is>
@@ -4427,146 +4431,146 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
         </is>
       </c>
       <c r="B114" s="14" t="n">
-        <v>226114831</v>
-      </c>
-      <c r="C114" s="15" t="n">
-        <v>327</v>
-      </c>
-      <c r="D114" s="15" t="n">
-        <v>34</v>
-      </c>
-      <c r="E114" s="14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F114" s="15" t="n">
-        <v>51</v>
-      </c>
-      <c r="G114" s="15" t="n">
-        <v>1341</v>
-      </c>
-      <c r="H114" s="15" t="n">
-        <v>243</v>
-      </c>
-      <c r="I114" s="15" t="n">
-        <v>68391</v>
-      </c>
-      <c r="J114" s="15" t="n">
-        <v>12393</v>
+        <v>226115478</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>1130</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>23730</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>3003</v>
       </c>
       <c r="K114" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
+          <t>PETITFEE - MASK 5 (блек, агава, какао, артишок, голд снейл)</t>
         </is>
       </c>
       <c r="B115" s="14" t="n">
-        <v>226115141</v>
-      </c>
-      <c r="C115" s="15" t="n">
-        <v>273</v>
-      </c>
-      <c r="D115" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="E115" s="14" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="F115" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="G115" s="15" t="n">
-        <v>1148</v>
-      </c>
-      <c r="H115" s="15" t="n">
-        <v>143</v>
-      </c>
-      <c r="I115" s="15" t="n">
-        <v>29848</v>
-      </c>
-      <c r="J115" s="15" t="n">
-        <v>3718</v>
+        <v>1177994944</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>1164</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>10476</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>1314</v>
       </c>
       <c r="K115" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PETITFEE - MASK 5 (блек, агава, какао, артишок, голд снейл)</t>
+          <t>PETITFEE - MASK 6 (блек, агава, какао, артишок, голд, ромашка)</t>
         </is>
       </c>
       <c r="B116" s="14" t="n">
-        <v>1177994944</v>
-      </c>
-      <c r="C116" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D116" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="E116" s="14" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F116" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="G116" s="15" t="n">
-        <v>1164</v>
-      </c>
-      <c r="H116" s="15" t="n">
-        <v>146</v>
-      </c>
-      <c r="I116" s="15" t="n">
-        <v>10476</v>
-      </c>
-      <c r="J116" s="15" t="n">
-        <v>1314</v>
+        <v>1175175447</v>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>1376</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>4128</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>534</v>
       </c>
       <c r="K116" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="16" t="inlineStr">
+      <c r="A117" s="15" t="inlineStr">
         <is>
           <t>ИТОГО PETITFEE/PETITFEE-FACEMASK</t>
         </is>
       </c>
-      <c r="B117" s="17" t="n"/>
-      <c r="C117" s="18" t="n">
+      <c r="B117" s="16" t="n"/>
+      <c r="C117" s="17" t="n">
         <v>2767</v>
       </c>
-      <c r="D117" s="18" t="n">
-        <v>439</v>
-      </c>
-      <c r="E117" s="17" t="n"/>
-      <c r="F117" s="18" t="n">
-        <v>660</v>
-      </c>
-      <c r="G117" s="17" t="n"/>
-      <c r="H117" s="17" t="n"/>
-      <c r="I117" s="18" t="n">
-        <v>793669</v>
-      </c>
-      <c r="J117" s="18" t="n">
-        <v>103677</v>
-      </c>
-      <c r="K117" s="17" t="n"/>
+      <c r="D117" s="17" t="n">
+        <v>205</v>
+      </c>
+      <c r="E117" s="16" t="n"/>
+      <c r="F117" s="17" t="n">
+        <v>217</v>
+      </c>
+      <c r="G117" s="16" t="n"/>
+      <c r="H117" s="16" t="n"/>
+      <c r="I117" s="17" t="n">
+        <v>262029</v>
+      </c>
+      <c r="J117" s="17" t="n">
+        <v>35832</v>
+      </c>
+      <c r="K117" s="16" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
@@ -4586,41 +4590,41 @@
       <c r="K118" s="13" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="19" t="inlineStr">
+      <c r="A119" s="18" t="inlineStr">
         <is>
           <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
         </is>
       </c>
-      <c r="B119" s="19" t="n">
+      <c r="B119" s="18" t="n">
         <v>437154709</v>
       </c>
-      <c r="C119" s="20" t="n">
+      <c r="C119" s="19" t="n">
         <v>5499</v>
       </c>
-      <c r="D119" s="20" t="n">
-        <v>425</v>
+      <c r="D119" s="19" t="n">
+        <v>964</v>
       </c>
       <c r="E119" s="19" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F119" s="20" t="n">
-        <v>638</v>
-      </c>
-      <c r="G119" s="20" t="n">
+        <v>2159</v>
+      </c>
+      <c r="F119" s="19" t="n">
+        <v>964</v>
+      </c>
+      <c r="G119" s="19" t="n">
         <v>1178</v>
       </c>
-      <c r="H119" s="20" t="n">
+      <c r="H119" s="19" t="n">
         <v>139</v>
       </c>
-      <c r="I119" s="20" t="n">
-        <v>751564</v>
-      </c>
-      <c r="J119" s="20" t="n">
-        <v>88682</v>
-      </c>
-      <c r="K119" s="19" t="inlineStr">
-        <is>
-          <t>Затоварка — акцент рекламы</t>
+      <c r="I119" s="19" t="n">
+        <v>1135592</v>
+      </c>
+      <c r="J119" s="19" t="n">
+        <v>133996</v>
+      </c>
+      <c r="K119" s="18" t="inlineStr">
+        <is>
+          <t>★ Драйвер</t>
         </is>
       </c>
     </row>
@@ -4633,33 +4637,33 @@
       <c r="B120" s="14" t="n">
         <v>437190353</v>
       </c>
-      <c r="C120" s="15" t="n">
+      <c r="C120" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="D120" s="15" t="n">
-        <v>31</v>
-      </c>
-      <c r="E120" s="14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F120" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="G120" s="15" t="n">
+      <c r="D120" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="G120" s="5" t="n">
         <v>2469</v>
       </c>
-      <c r="H120" s="15" t="n">
+      <c r="H120" s="5" t="n">
         <v>328</v>
       </c>
-      <c r="I120" s="15" t="n">
-        <v>113574</v>
-      </c>
-      <c r="J120" s="15" t="n">
-        <v>15088</v>
+      <c r="I120" s="5" t="n">
+        <v>251838</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>33456</v>
       </c>
       <c r="K120" s="14" t="inlineStr">
         <is>
-          <t>Рабочий</t>
+          <t>Ограничено остатком</t>
         </is>
       </c>
     </row>
@@ -4672,33 +4676,33 @@
       <c r="B121" s="14" t="n">
         <v>437242640</v>
       </c>
-      <c r="C121" s="15" t="n">
+      <c r="C121" s="5" t="n">
         <v>1201</v>
       </c>
-      <c r="D121" s="15" t="n">
-        <v>29</v>
-      </c>
-      <c r="E121" s="14" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="F121" s="15" t="n">
-        <v>44</v>
-      </c>
-      <c r="G121" s="15" t="n">
+      <c r="D121" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G121" s="5" t="n">
         <v>1341</v>
       </c>
-      <c r="H121" s="15" t="n">
+      <c r="H121" s="5" t="n">
         <v>239</v>
       </c>
-      <c r="I121" s="15" t="n">
-        <v>59004</v>
-      </c>
-      <c r="J121" s="15" t="n">
-        <v>10516</v>
+      <c r="I121" s="5" t="n">
+        <v>60345</v>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>10755</v>
       </c>
       <c r="K121" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -4711,29 +4715,29 @@
       <c r="B122" s="14" t="n">
         <v>437776835</v>
       </c>
-      <c r="C122" s="15" t="n">
+      <c r="C122" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D122" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E122" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F122" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G122" s="15" t="n">
+      <c r="D122" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G122" s="5" t="n">
         <v>1890</v>
       </c>
-      <c r="H122" s="15" t="n">
+      <c r="H122" s="5" t="n">
         <v>246</v>
       </c>
-      <c r="I122" s="15" t="n">
-        <v>9450</v>
-      </c>
-      <c r="J122" s="15" t="n">
-        <v>1230</v>
+      <c r="I122" s="5" t="n">
+        <v>7560</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>984</v>
       </c>
       <c r="K122" s="14" t="inlineStr">
         <is>
@@ -4750,62 +4754,62 @@
       <c r="B123" s="14" t="n">
         <v>1123574113</v>
       </c>
-      <c r="C123" s="15" t="n">
+      <c r="C123" s="5" t="n">
         <v>802</v>
       </c>
-      <c r="D123" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E123" s="14" t="n">
-        <v>401</v>
-      </c>
-      <c r="F123" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G123" s="15" t="n">
+      <c r="D123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="5" t="n">
         <v>1509</v>
       </c>
-      <c r="H123" s="15" t="n">
+      <c r="H123" s="5" t="n">
         <v>369</v>
       </c>
-      <c r="I123" s="15" t="n">
-        <v>4527</v>
-      </c>
-      <c r="J123" s="15" t="n">
-        <v>1107</v>
+      <c r="I123" s="5" t="n">
+        <v>1509</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>369</v>
       </c>
       <c r="K123" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="16" t="inlineStr">
+      <c r="A124" s="15" t="inlineStr">
         <is>
           <t>ИТОГО ROUND LAB</t>
         </is>
       </c>
-      <c r="B124" s="17" t="n"/>
-      <c r="C124" s="18" t="n">
+      <c r="B124" s="16" t="n"/>
+      <c r="C124" s="17" t="n">
         <v>7609</v>
       </c>
-      <c r="D124" s="18" t="n">
-        <v>494</v>
-      </c>
-      <c r="E124" s="17" t="n"/>
-      <c r="F124" s="18" t="n">
-        <v>736</v>
-      </c>
-      <c r="G124" s="17" t="n"/>
-      <c r="H124" s="17" t="n"/>
-      <c r="I124" s="18" t="n">
-        <v>938119</v>
-      </c>
-      <c r="J124" s="18" t="n">
-        <v>116623</v>
-      </c>
-      <c r="K124" s="17" t="n"/>
+      <c r="D124" s="17" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E124" s="16" t="n"/>
+      <c r="F124" s="17" t="n">
+        <v>1116</v>
+      </c>
+      <c r="G124" s="16" t="n"/>
+      <c r="H124" s="16" t="n"/>
+      <c r="I124" s="17" t="n">
+        <v>1456844</v>
+      </c>
+      <c r="J124" s="17" t="n">
+        <v>179560</v>
+      </c>
+      <c r="K124" s="16" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
@@ -4833,33 +4837,33 @@
       <c r="B126" s="14" t="n">
         <v>214312149</v>
       </c>
-      <c r="C126" s="15" t="n">
+      <c r="C126" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D126" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E126" s="14" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="F126" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G126" s="15" t="n">
+      <c r="D126" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G126" s="5" t="n">
         <v>1029</v>
       </c>
-      <c r="H126" s="15" t="n">
+      <c r="H126" s="5" t="n">
         <v>267</v>
       </c>
-      <c r="I126" s="15" t="n">
-        <v>4116</v>
-      </c>
-      <c r="J126" s="15" t="n">
-        <v>1068</v>
+      <c r="I126" s="5" t="n">
+        <v>19551</v>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>5073</v>
       </c>
       <c r="K126" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -4872,62 +4876,62 @@
       <c r="B127" s="14" t="n">
         <v>214311963</v>
       </c>
-      <c r="C127" s="15" t="n">
+      <c r="C127" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D127" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E127" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="F127" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G127" s="15" t="n">
+      <c r="D127" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G127" s="5" t="n">
         <v>1445</v>
       </c>
-      <c r="H127" s="15" t="n">
+      <c r="H127" s="5" t="n">
         <v>444</v>
       </c>
-      <c r="I127" s="15" t="n">
-        <v>4335</v>
-      </c>
-      <c r="J127" s="15" t="n">
-        <v>1332</v>
+      <c r="I127" s="5" t="n">
+        <v>10115</v>
+      </c>
+      <c r="J127" s="5" t="n">
+        <v>3108</v>
       </c>
       <c r="K127" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="16" t="inlineStr">
+      <c r="A128" s="15" t="inlineStr">
         <is>
           <t>ИТОГО SKIN1004</t>
         </is>
       </c>
-      <c r="B128" s="17" t="n"/>
-      <c r="C128" s="18" t="n">
+      <c r="B128" s="16" t="n"/>
+      <c r="C128" s="17" t="n">
         <v>52</v>
       </c>
-      <c r="D128" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E128" s="17" t="n"/>
-      <c r="F128" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="G128" s="17" t="n"/>
-      <c r="H128" s="17" t="n"/>
-      <c r="I128" s="18" t="n">
-        <v>8451</v>
-      </c>
-      <c r="J128" s="18" t="n">
-        <v>2400</v>
-      </c>
-      <c r="K128" s="17" t="n"/>
+      <c r="D128" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="E128" s="16" t="n"/>
+      <c r="F128" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G128" s="16" t="n"/>
+      <c r="H128" s="16" t="n"/>
+      <c r="I128" s="17" t="n">
+        <v>29666</v>
+      </c>
+      <c r="J128" s="17" t="n">
+        <v>8181</v>
+      </c>
+      <c r="K128" s="16" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="inlineStr">
@@ -4949,105 +4953,107 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="n">
+        <v>248929125</v>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>2382</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>317</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>57168</v>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>7608</v>
+      </c>
+      <c r="K130" s="14" t="inlineStr">
+        <is>
+          <t>Рабочий</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="14" t="inlineStr">
+        <is>
           <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar [106g] / Мыло для проблемной кожи с aha bha кислотами</t>
         </is>
       </c>
-      <c r="B130" s="14" t="n">
+      <c r="B131" s="14" t="n">
         <v>248928046</v>
       </c>
-      <c r="C130" s="15" t="n">
+      <c r="C131" s="5" t="n">
         <v>525</v>
       </c>
-      <c r="D130" s="15" t="n">
+      <c r="D131" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E131" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E130" s="14" t="n">
-        <v>175</v>
-      </c>
-      <c r="F130" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G130" s="15" t="n">
+      <c r="F131" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G131" s="5" t="n">
         <v>1287</v>
       </c>
-      <c r="H130" s="15" t="n">
+      <c r="H131" s="5" t="n">
         <v>165</v>
       </c>
-      <c r="I130" s="15" t="n">
-        <v>5148</v>
-      </c>
-      <c r="J130" s="15" t="n">
-        <v>660</v>
-      </c>
-      <c r="K130" s="14" t="inlineStr">
-        <is>
-          <t>Затоварка — акцент рекламы</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="21" t="inlineStr">
-        <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
-        </is>
-      </c>
-      <c r="B131" s="21" t="n">
-        <v>248929125</v>
-      </c>
-      <c r="C131" s="22" t="n">
-        <v>55</v>
-      </c>
-      <c r="D131" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="21" t="n"/>
-      <c r="F131" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="22" t="n">
-        <v>2382</v>
-      </c>
-      <c r="H131" s="22" t="n">
-        <v>317</v>
-      </c>
-      <c r="I131" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" s="21" t="inlineStr">
-        <is>
-          <t>Нет продаж — разогнать/распродать</t>
+      <c r="I131" s="5" t="n">
+        <v>14157</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>1815</v>
+      </c>
+      <c r="K131" s="14" t="inlineStr">
+        <is>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="16" t="inlineStr">
+      <c r="A132" s="15" t="inlineStr">
         <is>
           <t>ИТОГО SOMEBYMI</t>
         </is>
       </c>
-      <c r="B132" s="17" t="n"/>
-      <c r="C132" s="18" t="n">
+      <c r="B132" s="16" t="n"/>
+      <c r="C132" s="17" t="n">
         <v>580</v>
       </c>
-      <c r="D132" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E132" s="17" t="n"/>
-      <c r="F132" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="G132" s="17" t="n"/>
-      <c r="H132" s="17" t="n"/>
-      <c r="I132" s="18" t="n">
-        <v>5148</v>
-      </c>
-      <c r="J132" s="18" t="n">
-        <v>660</v>
-      </c>
-      <c r="K132" s="17" t="n"/>
+      <c r="D132" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E132" s="16" t="n"/>
+      <c r="F132" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="G132" s="16" t="n"/>
+      <c r="H132" s="16" t="n"/>
+      <c r="I132" s="17" t="n">
+        <v>71325</v>
+      </c>
+      <c r="J132" s="17" t="n">
+        <v>9423</v>
+      </c>
+      <c r="K132" s="16" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="inlineStr">
@@ -5075,33 +5081,33 @@
       <c r="B134" s="14" t="n">
         <v>214312385</v>
       </c>
-      <c r="C134" s="15" t="n">
+      <c r="C134" s="5" t="n">
         <v>115</v>
       </c>
-      <c r="D134" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E134" s="14" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F134" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="G134" s="15" t="n">
+      <c r="D134" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G134" s="5" t="n">
         <v>1637</v>
       </c>
-      <c r="H134" s="15" t="n">
+      <c r="H134" s="5" t="n">
         <v>217</v>
       </c>
-      <c r="I134" s="15" t="n">
-        <v>19644</v>
-      </c>
-      <c r="J134" s="15" t="n">
-        <v>2604</v>
+      <c r="I134" s="5" t="n">
+        <v>21281</v>
+      </c>
+      <c r="J134" s="5" t="n">
+        <v>2821</v>
       </c>
       <c r="K134" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -5114,62 +5120,62 @@
       <c r="B135" s="14" t="n">
         <v>247275092</v>
       </c>
-      <c r="C135" s="15" t="n">
+      <c r="C135" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="D135" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E135" s="14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F135" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="G135" s="15" t="n">
+      <c r="D135" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G135" s="5" t="n">
         <v>1964</v>
       </c>
-      <c r="H135" s="15" t="n">
+      <c r="H135" s="5" t="n">
         <v>278</v>
       </c>
-      <c r="I135" s="15" t="n">
-        <v>11784</v>
-      </c>
-      <c r="J135" s="15" t="n">
-        <v>1668</v>
+      <c r="I135" s="5" t="n">
+        <v>15712</v>
+      </c>
+      <c r="J135" s="5" t="n">
+        <v>2224</v>
       </c>
       <c r="K135" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="16" t="inlineStr">
+      <c r="A136" s="15" t="inlineStr">
         <is>
           <t>ИТОГО TheOrdinary</t>
         </is>
       </c>
-      <c r="B136" s="17" t="n"/>
-      <c r="C136" s="18" t="n">
+      <c r="B136" s="16" t="n"/>
+      <c r="C136" s="17" t="n">
         <v>140</v>
       </c>
-      <c r="D136" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="E136" s="17" t="n"/>
-      <c r="F136" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="G136" s="17" t="n"/>
-      <c r="H136" s="17" t="n"/>
-      <c r="I136" s="18" t="n">
-        <v>31428</v>
-      </c>
-      <c r="J136" s="18" t="n">
-        <v>4272</v>
-      </c>
-      <c r="K136" s="17" t="n"/>
+      <c r="D136" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="E136" s="16" t="n"/>
+      <c r="F136" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G136" s="16" t="n"/>
+      <c r="H136" s="16" t="n"/>
+      <c r="I136" s="17" t="n">
+        <v>36993</v>
+      </c>
+      <c r="J136" s="17" t="n">
+        <v>5045</v>
+      </c>
+      <c r="K136" s="16" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
@@ -5189,197 +5195,197 @@
       <c r="K137" s="13" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="19" t="inlineStr">
+      <c r="A138" s="18" t="inlineStr">
         <is>
           <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
         </is>
       </c>
-      <c r="B138" s="19" t="n">
+      <c r="B138" s="18" t="n">
         <v>868516027</v>
       </c>
-      <c r="C138" s="20" t="n">
+      <c r="C138" s="19" t="n">
         <v>15980</v>
       </c>
-      <c r="D138" s="20" t="n">
-        <v>426</v>
+      <c r="D138" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="E138" s="19" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="F138" s="20" t="n">
-        <v>639</v>
-      </c>
-      <c r="G138" s="20" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F138" s="19" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G138" s="19" t="n">
         <v>1586</v>
       </c>
-      <c r="H138" s="20" t="n">
+      <c r="H138" s="19" t="n">
         <v>199</v>
       </c>
-      <c r="I138" s="20" t="n">
-        <v>1013454</v>
-      </c>
-      <c r="J138" s="20" t="n">
-        <v>127161</v>
-      </c>
-      <c r="K138" s="19" t="inlineStr">
-        <is>
-          <t>Затоварка — акцент рекламы</t>
+      <c r="I138" s="19" t="n">
+        <v>4995900</v>
+      </c>
+      <c r="J138" s="19" t="n">
+        <v>626850</v>
+      </c>
+      <c r="K138" s="18" t="inlineStr">
+        <is>
+          <t>★ Драйвер</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="14" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
         </is>
       </c>
       <c r="B139" s="14" t="n">
-        <v>551465879</v>
-      </c>
-      <c r="C139" s="15" t="n">
-        <v>2217</v>
-      </c>
-      <c r="D139" s="15" t="n">
-        <v>81</v>
-      </c>
-      <c r="E139" s="14" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="F139" s="15" t="n">
-        <v>122</v>
-      </c>
-      <c r="G139" s="15" t="n">
-        <v>1445</v>
-      </c>
-      <c r="H139" s="15" t="n">
-        <v>291</v>
-      </c>
-      <c r="I139" s="15" t="n">
-        <v>176290</v>
-      </c>
-      <c r="J139" s="15" t="n">
-        <v>35502</v>
+        <v>551607905</v>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>1456</v>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>1620</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>200880</v>
+      </c>
+      <c r="J139" s="5" t="n">
+        <v>26288</v>
       </c>
       <c r="K139" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
         </is>
       </c>
       <c r="B140" s="14" t="n">
-        <v>551607905</v>
-      </c>
-      <c r="C140" s="15" t="n">
-        <v>1456</v>
-      </c>
-      <c r="D140" s="15" t="n">
-        <v>36</v>
-      </c>
-      <c r="E140" s="14" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="F140" s="15" t="n">
-        <v>54</v>
-      </c>
-      <c r="G140" s="15" t="n">
-        <v>1620</v>
-      </c>
-      <c r="H140" s="15" t="n">
-        <v>212</v>
-      </c>
-      <c r="I140" s="15" t="n">
-        <v>87480</v>
-      </c>
-      <c r="J140" s="15" t="n">
-        <v>11448</v>
+        <v>551540924</v>
+      </c>
+      <c r="C140" s="5" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>1445</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>255</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>46240</v>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>8160</v>
       </c>
       <c r="K140" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="14" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
         </is>
       </c>
       <c r="B141" s="14" t="n">
-        <v>551387355</v>
-      </c>
-      <c r="C141" s="15" t="n">
-        <v>8728</v>
-      </c>
-      <c r="D141" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="E141" s="14" t="n">
-        <v>379.5</v>
-      </c>
-      <c r="F141" s="15" t="n">
-        <v>34</v>
-      </c>
-      <c r="G141" s="15" t="n">
-        <v>1187</v>
-      </c>
-      <c r="H141" s="15" t="n">
-        <v>154</v>
-      </c>
-      <c r="I141" s="15" t="n">
-        <v>40358</v>
-      </c>
-      <c r="J141" s="15" t="n">
-        <v>5236</v>
+        <v>551472457</v>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>1761</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>229</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>24654</v>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>3206</v>
       </c>
       <c r="K141" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
         </is>
       </c>
       <c r="B142" s="14" t="n">
-        <v>551600265</v>
-      </c>
-      <c r="C142" s="15" t="n">
-        <v>1296</v>
-      </c>
-      <c r="D142" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E142" s="14" t="n">
-        <v>324</v>
-      </c>
-      <c r="F142" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="G142" s="15" t="n">
-        <v>406</v>
-      </c>
-      <c r="H142" s="15" t="n">
-        <v>105</v>
-      </c>
-      <c r="I142" s="15" t="n">
-        <v>2436</v>
-      </c>
-      <c r="J142" s="15" t="n">
-        <v>630</v>
+        <v>551387355</v>
+      </c>
+      <c r="C142" s="5" t="n">
+        <v>8728</v>
+      </c>
+      <c r="D142" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>1187</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>9496</v>
+      </c>
+      <c r="J142" s="5" t="n">
+        <v>1232</v>
       </c>
       <c r="K142" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -5392,111 +5398,111 @@
       <c r="B143" s="14" t="n">
         <v>551392965</v>
       </c>
-      <c r="C143" s="15" t="n">
+      <c r="C143" s="5" t="n">
         <v>353</v>
       </c>
-      <c r="D143" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E143" s="14" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="F143" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="G143" s="15" t="n">
+      <c r="D143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G143" s="5" t="n">
         <v>1967</v>
       </c>
-      <c r="H143" s="15" t="n">
+      <c r="H143" s="5" t="n">
         <v>259</v>
       </c>
-      <c r="I143" s="15" t="n">
-        <v>11802</v>
-      </c>
-      <c r="J143" s="15" t="n">
-        <v>1554</v>
+      <c r="I143" s="5" t="n">
+        <v>13769</v>
+      </c>
+      <c r="J143" s="5" t="n">
+        <v>1813</v>
       </c>
       <c r="K143" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выравнивания тона и рельефа кожи лица</t>
         </is>
       </c>
       <c r="B144" s="14" t="n">
-        <v>551518955</v>
-      </c>
-      <c r="C144" s="15" t="n">
-        <v>24</v>
-      </c>
-      <c r="D144" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E144" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="F144" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G144" s="15" t="n">
-        <v>1678</v>
-      </c>
-      <c r="H144" s="15" t="n">
-        <v>216</v>
-      </c>
-      <c r="I144" s="15" t="n">
-        <v>6712</v>
-      </c>
-      <c r="J144" s="15" t="n">
-        <v>864</v>
+        <v>551447345</v>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>1860</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>463</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>11160</v>
+      </c>
+      <c r="J144" s="5" t="n">
+        <v>2778</v>
       </c>
       <c r="K144" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="14" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
         </is>
       </c>
       <c r="B145" s="14" t="n">
-        <v>551540924</v>
-      </c>
-      <c r="C145" s="15" t="n">
-        <v>1375</v>
-      </c>
-      <c r="D145" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E145" s="14" t="n">
-        <v>687.5</v>
-      </c>
-      <c r="F145" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G145" s="15" t="n">
-        <v>1445</v>
-      </c>
-      <c r="H145" s="15" t="n">
-        <v>255</v>
-      </c>
-      <c r="I145" s="15" t="n">
-        <v>4335</v>
-      </c>
-      <c r="J145" s="15" t="n">
-        <v>765</v>
+        <v>551600265</v>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>1296</v>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>406</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>2030</v>
+      </c>
+      <c r="J145" s="5" t="n">
+        <v>525</v>
       </c>
       <c r="K145" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -5509,140 +5515,140 @@
       <c r="B146" s="14" t="n">
         <v>551482493</v>
       </c>
-      <c r="C146" s="15" t="n">
+      <c r="C146" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="D146" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E146" s="14" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F146" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G146" s="15" t="n">
+      <c r="D146" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G146" s="5" t="n">
         <v>1757</v>
       </c>
-      <c r="H146" s="15" t="n">
+      <c r="H146" s="5" t="n">
         <v>308</v>
       </c>
-      <c r="I146" s="15" t="n">
-        <v>5271</v>
-      </c>
-      <c r="J146" s="15" t="n">
-        <v>924</v>
+      <c r="I146" s="5" t="n">
+        <v>8785</v>
+      </c>
+      <c r="J146" s="5" t="n">
+        <v>1540</v>
       </c>
       <c r="K146" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="14" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выравнивания тона и рельефа кожи лица</t>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
         </is>
       </c>
       <c r="B147" s="14" t="n">
-        <v>551447345</v>
-      </c>
-      <c r="C147" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="D147" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" s="14" t="n">
-        <v>13</v>
-      </c>
-      <c r="F147" s="15" t="n">
+        <v>551465879</v>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>2217</v>
+      </c>
+      <c r="D147" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G147" s="15" t="n">
-        <v>1860</v>
-      </c>
-      <c r="H147" s="15" t="n">
-        <v>463</v>
-      </c>
-      <c r="I147" s="15" t="n">
-        <v>3720</v>
-      </c>
-      <c r="J147" s="15" t="n">
-        <v>926</v>
+      <c r="E147" s="5" t="n">
+        <v>586</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>1445</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>291</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>2890</v>
+      </c>
+      <c r="J147" s="5" t="n">
+        <v>582</v>
       </c>
       <c r="K147" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
         </is>
       </c>
       <c r="B148" s="14" t="n">
-        <v>551472457</v>
-      </c>
-      <c r="C148" s="15" t="n">
-        <v>35</v>
-      </c>
-      <c r="D148" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" s="14" t="n">
-        <v>35</v>
-      </c>
-      <c r="F148" s="15" t="n">
+        <v>551518955</v>
+      </c>
+      <c r="C148" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G148" s="15" t="n">
-        <v>1761</v>
-      </c>
-      <c r="H148" s="15" t="n">
-        <v>229</v>
-      </c>
-      <c r="I148" s="15" t="n">
-        <v>3522</v>
-      </c>
-      <c r="J148" s="15" t="n">
-        <v>458</v>
+      <c r="F148" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>1678</v>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>3356</v>
+      </c>
+      <c r="J148" s="5" t="n">
+        <v>432</v>
       </c>
       <c r="K148" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="16" t="inlineStr">
+      <c r="A149" s="15" t="inlineStr">
         <is>
           <t>ИТОГО CELIMAX</t>
         </is>
       </c>
-      <c r="B149" s="17" t="n"/>
-      <c r="C149" s="18" t="n">
+      <c r="B149" s="16" t="n"/>
+      <c r="C149" s="17" t="n">
         <v>31554</v>
       </c>
-      <c r="D149" s="18" t="n">
-        <v>583</v>
-      </c>
-      <c r="E149" s="17" t="n"/>
-      <c r="F149" s="18" t="n">
-        <v>875</v>
-      </c>
-      <c r="G149" s="17" t="n"/>
-      <c r="H149" s="17" t="n"/>
-      <c r="I149" s="18" t="n">
-        <v>1355380</v>
-      </c>
-      <c r="J149" s="18" t="n">
-        <v>185468</v>
-      </c>
-      <c r="K149" s="17" t="n"/>
+      <c r="D149" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E149" s="16" t="n"/>
+      <c r="F149" s="17" t="n">
+        <v>3355</v>
+      </c>
+      <c r="G149" s="16" t="n"/>
+      <c r="H149" s="16" t="n"/>
+      <c r="I149" s="17" t="n">
+        <v>5319160</v>
+      </c>
+      <c r="J149" s="17" t="n">
+        <v>673406</v>
+      </c>
+      <c r="K149" s="16" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
@@ -5670,33 +5676,33 @@
       <c r="B151" s="14" t="n">
         <v>1119249556</v>
       </c>
-      <c r="C151" s="15" t="n">
+      <c r="C151" s="5" t="n">
         <v>1008</v>
       </c>
-      <c r="D151" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E151" s="14" t="n">
-        <v>252</v>
-      </c>
-      <c r="F151" s="15" t="n">
+      <c r="D151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="G151" s="15" t="n">
+      <c r="G151" s="5" t="n">
         <v>2964</v>
       </c>
-      <c r="H151" s="15" t="n">
+      <c r="H151" s="5" t="n">
         <v>401</v>
       </c>
-      <c r="I151" s="15" t="n">
+      <c r="I151" s="5" t="n">
         <v>17784</v>
       </c>
-      <c r="J151" s="15" t="n">
+      <c r="J151" s="5" t="n">
         <v>2406</v>
       </c>
       <c r="K151" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
@@ -5709,62 +5715,62 @@
       <c r="B152" s="14" t="n">
         <v>1123494802</v>
       </c>
-      <c r="C152" s="15" t="n">
+      <c r="C152" s="5" t="n">
         <v>397</v>
       </c>
-      <c r="D152" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" s="14" t="n">
-        <v>397</v>
-      </c>
-      <c r="F152" s="15" t="n">
+      <c r="D152" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G152" s="15" t="n">
+      <c r="G152" s="5" t="n">
         <v>2148</v>
       </c>
-      <c r="H152" s="15" t="n">
+      <c r="H152" s="5" t="n">
         <v>292</v>
       </c>
-      <c r="I152" s="15" t="n">
+      <c r="I152" s="5" t="n">
         <v>4296</v>
       </c>
-      <c r="J152" s="15" t="n">
+      <c r="J152" s="5" t="n">
         <v>584</v>
       </c>
       <c r="K152" s="14" t="inlineStr">
         <is>
-          <t>Затоварка — акцент рекламы</t>
+          <t>Рабочий</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="16" t="inlineStr">
+      <c r="A153" s="15" t="inlineStr">
         <is>
           <t>ИТОГО VT</t>
         </is>
       </c>
-      <c r="B153" s="17" t="n"/>
-      <c r="C153" s="18" t="n">
+      <c r="B153" s="16" t="n"/>
+      <c r="C153" s="17" t="n">
         <v>1405</v>
       </c>
-      <c r="D153" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E153" s="17" t="n"/>
-      <c r="F153" s="18" t="n">
+      <c r="D153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="16" t="n"/>
+      <c r="F153" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="G153" s="17" t="n"/>
-      <c r="H153" s="17" t="n"/>
-      <c r="I153" s="18" t="n">
+      <c r="G153" s="16" t="n"/>
+      <c r="H153" s="16" t="n"/>
+      <c r="I153" s="17" t="n">
         <v>22080</v>
       </c>
-      <c r="J153" s="18" t="n">
+      <c r="J153" s="17" t="n">
         <v>2990</v>
       </c>
-      <c r="K153" s="17" t="n"/>
+      <c r="K153" s="16" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
@@ -5777,19 +5783,19 @@
         <v>107901</v>
       </c>
       <c r="D155" s="8" t="n">
-        <v>6452</v>
+        <v>12884</v>
       </c>
       <c r="E155" s="7" t="n"/>
       <c r="F155" s="8" t="n">
-        <v>9258</v>
+        <v>16768</v>
       </c>
       <c r="G155" s="7" t="n"/>
       <c r="H155" s="7" t="n"/>
       <c r="I155" s="8" t="n">
-        <v>9512287</v>
+        <v>18635536</v>
       </c>
       <c r="J155" s="8" t="n">
-        <v>1629530</v>
+        <v>3273713</v>
       </c>
       <c r="K155" s="7" t="n"/>
     </row>
@@ -5804,24 +5810,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>ДЕДЫ МОРОЗЫ — ПЛАН ОКТЯБРЬ (отдельно)</t>
         </is>
@@ -5830,62 +5835,57 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Цель — прибыль 350 ₽/шт (как ты задал). Ставки факт: комиссия 38,5%, эквайринг 2,82%, налог 1%, логистика по SKU, ДРР 10%. Октябрь — старт сезона, пик продаж ноя–дек.</t>
+          <t>Прибыль 350 ₽/шт. Комиссия 38,5%, налог 1%, логистика по SKU, ДРР 10%. Октябрь — старт, пик ноя-дек. Цену 10 000 ₽ снизить до рыночной (в таблице).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>Себес ₽ (+60 ФФ)</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Себес ₽(+ФФ)</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Логистика ₽</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>Остаток WB шт</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>Остаток WB</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Цена до СПП ₽</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Цена с СПП ₽</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
-        <is>
-          <t>Комиссия 38,5% ₽</t>
-        </is>
-      </c>
-      <c r="H4" s="24" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t>Маржа ₽/ед</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t>ROI %</t>
         </is>
       </c>
-      <c r="J4" s="24" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>ПЛАН окт шт</t>
         </is>
       </c>
-      <c r="K4" s="24" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t>План прибыль ₽</t>
         </is>
@@ -5895,34 +5895,31 @@
       <c r="A5" s="14" t="n">
         <v>48905926</v>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="5" t="n">
         <v>352</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="5" t="n">
         <v>279</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="5" t="n">
         <v>496</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="5" t="n">
         <v>2058</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="5" t="n">
         <v>1342</v>
       </c>
-      <c r="G5" s="15" t="n">
-        <v>792</v>
-      </c>
-      <c r="H5" s="15" t="n">
+      <c r="G5" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H5" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="I5" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="J5" s="14" t="n">
         <v>74</v>
       </c>
-      <c r="K5" s="15" t="n">
+      <c r="J5" s="5" t="n">
         <v>25900</v>
       </c>
     </row>
@@ -5930,34 +5927,31 @@
       <c r="A6" s="14" t="n">
         <v>48906308</v>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="5" t="n">
         <v>352</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="5" t="n">
         <v>279</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="5" t="n">
         <v>2058</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="5" t="n">
         <v>1342</v>
       </c>
-      <c r="G6" s="15" t="n">
-        <v>792</v>
-      </c>
-      <c r="H6" s="15" t="n">
+      <c r="G6" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H6" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="I6" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="J6" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K6" s="15" t="n">
+      <c r="J6" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -5965,34 +5959,31 @@
       <c r="A7" s="14" t="n">
         <v>48906952</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="5" t="n">
         <v>374</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="5" t="n">
         <v>279</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="5" t="n">
         <v>2105</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="5" t="n">
         <v>1373</v>
       </c>
-      <c r="G7" s="15" t="n">
-        <v>810</v>
-      </c>
-      <c r="H7" s="15" t="n">
+      <c r="G7" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H7" s="14" t="n">
+        <v>94</v>
+      </c>
       <c r="I7" s="14" t="n">
-        <v>94</v>
-      </c>
-      <c r="J7" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K7" s="15" t="n">
+      <c r="J7" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6000,34 +5991,31 @@
       <c r="A8" s="14" t="n">
         <v>48908708</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="5" t="n">
         <v>352</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="5" t="n">
         <v>279</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="5" t="n">
         <v>2058</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="5" t="n">
         <v>1342</v>
       </c>
-      <c r="G8" s="15" t="n">
-        <v>792</v>
-      </c>
-      <c r="H8" s="15" t="n">
+      <c r="G8" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H8" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="I8" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="J8" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K8" s="15" t="n">
+      <c r="J8" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6035,34 +6023,31 @@
       <c r="A9" s="14" t="n">
         <v>103431353</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="5" t="n">
         <v>352</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="5" t="n">
         <v>279</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="5" t="n">
         <v>2058</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="5" t="n">
         <v>1342</v>
       </c>
-      <c r="G9" s="15" t="n">
-        <v>792</v>
-      </c>
-      <c r="H9" s="15" t="n">
+      <c r="G9" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H9" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="I9" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="J9" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K9" s="15" t="n">
+      <c r="J9" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6070,34 +6055,31 @@
       <c r="A10" s="14" t="n">
         <v>103431810</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="5" t="n">
         <v>352</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="5" t="n">
         <v>279</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="5" t="n">
         <v>2058</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="5" t="n">
         <v>1342</v>
       </c>
-      <c r="G10" s="15" t="n">
-        <v>792</v>
-      </c>
-      <c r="H10" s="15" t="n">
+      <c r="G10" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H10" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="I10" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="J10" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K10" s="15" t="n">
+      <c r="J10" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6105,34 +6087,31 @@
       <c r="A11" s="14" t="n">
         <v>103441912</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="5" t="n">
         <v>352</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="5" t="n">
         <v>279</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="5" t="n">
         <v>2058</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="5" t="n">
         <v>1342</v>
       </c>
-      <c r="G11" s="15" t="n">
-        <v>792</v>
-      </c>
-      <c r="H11" s="15" t="n">
+      <c r="G11" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H11" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="I11" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="J11" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K11" s="15" t="n">
+      <c r="J11" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6140,34 +6119,31 @@
       <c r="A12" s="14" t="n">
         <v>104590122</v>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="5" t="n">
         <v>352</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="5" t="n">
         <v>279</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="5" t="n">
         <v>2058</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="F12" s="5" t="n">
         <v>1342</v>
       </c>
-      <c r="G12" s="15" t="n">
-        <v>792</v>
-      </c>
-      <c r="H12" s="15" t="n">
+      <c r="G12" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H12" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="I12" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="J12" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K12" s="15" t="n">
+      <c r="J12" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6175,34 +6151,31 @@
       <c r="A13" s="14" t="n">
         <v>555213580</v>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="5" t="n">
         <v>567</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="5" t="n">
         <v>428</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="5" t="n">
         <v>2821</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="5" t="n">
         <v>1839</v>
       </c>
-      <c r="G13" s="15" t="n">
-        <v>1086</v>
-      </c>
-      <c r="H13" s="15" t="n">
+      <c r="G13" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H13" s="14" t="n">
+        <v>62</v>
+      </c>
       <c r="I13" s="14" t="n">
-        <v>62</v>
-      </c>
-      <c r="J13" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K13" s="15" t="n">
+      <c r="J13" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6210,34 +6183,31 @@
       <c r="A14" s="14" t="n">
         <v>190314011</v>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="5" t="n">
         <v>369</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="5" t="n">
         <v>215</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="5" t="n">
         <v>1958</v>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="F14" s="5" t="n">
         <v>1277</v>
       </c>
-      <c r="G14" s="15" t="n">
-        <v>754</v>
-      </c>
-      <c r="H14" s="15" t="n">
+      <c r="G14" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H14" s="14" t="n">
+        <v>95</v>
+      </c>
       <c r="I14" s="14" t="n">
-        <v>95</v>
-      </c>
-      <c r="J14" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K14" s="15" t="n">
+      <c r="J14" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6245,34 +6215,31 @@
       <c r="A15" s="14" t="n">
         <v>190314349</v>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="5" t="n">
         <v>364</v>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="5" t="n">
         <v>194</v>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="5" t="n">
         <v>1904</v>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F15" s="5" t="n">
         <v>1241</v>
       </c>
-      <c r="G15" s="15" t="n">
-        <v>733</v>
-      </c>
-      <c r="H15" s="15" t="n">
+      <c r="G15" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H15" s="14" t="n">
+        <v>96</v>
+      </c>
       <c r="I15" s="14" t="n">
-        <v>96</v>
-      </c>
-      <c r="J15" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K15" s="15" t="n">
+      <c r="J15" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6280,34 +6247,31 @@
       <c r="A16" s="14" t="n">
         <v>555208894</v>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="5" t="n">
         <v>567</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="5" t="n">
         <v>596</v>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="5" t="n">
         <v>3172</v>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="F16" s="5" t="n">
         <v>2068</v>
       </c>
-      <c r="G16" s="15" t="n">
-        <v>1221</v>
-      </c>
-      <c r="H16" s="15" t="n">
+      <c r="G16" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H16" s="14" t="n">
+        <v>62</v>
+      </c>
       <c r="I16" s="14" t="n">
-        <v>62</v>
-      </c>
-      <c r="J16" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K16" s="15" t="n">
+      <c r="J16" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6315,34 +6279,31 @@
       <c r="A17" s="14" t="n">
         <v>555134309</v>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="5" t="n">
         <v>512</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="5" t="n">
         <v>309</v>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="5" t="n">
         <v>2457</v>
       </c>
-      <c r="F17" s="15" t="n">
+      <c r="F17" s="5" t="n">
         <v>1602</v>
       </c>
-      <c r="G17" s="15" t="n">
-        <v>946</v>
-      </c>
-      <c r="H17" s="15" t="n">
+      <c r="G17" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H17" s="14" t="n">
+        <v>68</v>
+      </c>
       <c r="I17" s="14" t="n">
-        <v>68</v>
-      </c>
-      <c r="J17" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K17" s="15" t="n">
+      <c r="J17" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6350,34 +6311,31 @@
       <c r="A18" s="14" t="n">
         <v>555135716</v>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B18" s="5" t="n">
         <v>567</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="5" t="n">
         <v>596</v>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="5" t="n">
         <v>3172</v>
       </c>
-      <c r="F18" s="15" t="n">
+      <c r="F18" s="5" t="n">
         <v>2068</v>
       </c>
-      <c r="G18" s="15" t="n">
-        <v>1221</v>
-      </c>
-      <c r="H18" s="15" t="n">
+      <c r="G18" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H18" s="14" t="n">
+        <v>62</v>
+      </c>
       <c r="I18" s="14" t="n">
-        <v>62</v>
-      </c>
-      <c r="J18" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K18" s="15" t="n">
+      <c r="J18" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6385,34 +6343,31 @@
       <c r="A19" s="14" t="n">
         <v>555151552</v>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="5" t="n">
         <v>901</v>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="5" t="n">
         <v>885</v>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E19" s="5" t="n">
         <v>4479</v>
       </c>
-      <c r="F19" s="15" t="n">
+      <c r="F19" s="5" t="n">
         <v>2921</v>
       </c>
-      <c r="G19" s="15" t="n">
-        <v>1725</v>
-      </c>
-      <c r="H19" s="15" t="n">
+      <c r="G19" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H19" s="14" t="n">
+        <v>39</v>
+      </c>
       <c r="I19" s="14" t="n">
-        <v>39</v>
-      </c>
-      <c r="J19" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="K19" s="15" t="n">
+      <c r="J19" s="5" t="n">
         <v>13300</v>
       </c>
     </row>
@@ -6420,34 +6375,31 @@
       <c r="A20" s="14" t="n">
         <v>555204573</v>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="5" t="n">
         <v>512</v>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="5" t="n">
         <v>430</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="E20" s="5" t="n">
         <v>2710</v>
       </c>
-      <c r="F20" s="15" t="n">
+      <c r="F20" s="5" t="n">
         <v>1767</v>
       </c>
-      <c r="G20" s="15" t="n">
-        <v>1043</v>
-      </c>
-      <c r="H20" s="15" t="n">
+      <c r="G20" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H20" s="14" t="n">
+        <v>68</v>
+      </c>
       <c r="I20" s="14" t="n">
-        <v>68</v>
-      </c>
-      <c r="J20" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K20" s="15" t="n">
+      <c r="J20" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
@@ -6455,64 +6407,60 @@
       <c r="A21" s="14" t="n">
         <v>555212357</v>
       </c>
-      <c r="B21" s="15" t="n">
+      <c r="B21" s="5" t="n">
         <v>512</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="5" t="n">
         <v>309</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E21" s="5" t="n">
         <v>2457</v>
       </c>
-      <c r="F21" s="15" t="n">
+      <c r="F21" s="5" t="n">
         <v>1602</v>
       </c>
-      <c r="G21" s="15" t="n">
-        <v>946</v>
-      </c>
-      <c r="H21" s="15" t="n">
+      <c r="G21" s="5" t="n">
         <v>350</v>
       </c>
+      <c r="H21" s="14" t="n">
+        <v>68</v>
+      </c>
       <c r="I21" s="14" t="n">
-        <v>68</v>
-      </c>
-      <c r="J21" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="K21" s="15" t="n">
+      <c r="J21" s="5" t="n">
         <v>26250</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>ИТОГО ДЕДЫ МОРОЗЫ</t>
         </is>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="26" t="n">
+      <c r="D22" s="25" t="n">
         <v>8246</v>
       </c>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="26" t="n">
+      <c r="I22" s="25" t="n">
         <v>1237</v>
       </c>
-      <c r="K22" s="26" t="n">
+      <c r="J22" s="25" t="n">
         <v>432950</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>Остаток WB: 8,246 шт (+ склад/контейнер ~43 000 шт под сезон). Октябрь-план: 1,237 шт → прибыль 433 тыс ₽. Пик ноя-дек: при распродаже всего остатка WB прибыль ~2.89 млн ₽.</t>
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>Остаток WB 8,246 шт (+ ~43 000 склад/контейнер). Окт-план 1,237 шт → 433 тыс ₽. Пик ноя-дек: весь остаток WB ≈ 2.89 млн ₽.</t>
         </is>
       </c>
     </row>
@@ -6534,63 +6482,56 @@
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>ЭЛЕКТРОНИКА — РАСПРОДАЖА (отдельно)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>План — распродать и не закупать (решение собственника). Массажёр не продаём. Маржа — факт Ракеты.</t>
-        </is>
-      </c>
-    </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Артикул ВБ</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Товар</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>Себес ₽</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>Цена ₽</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
-        <is>
-          <t>Маржа ₽/ед (факт)</t>
-        </is>
-      </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>Маржа ₽/ед</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>ROI %</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>Остаток WB</t>
         </is>
       </c>
-      <c r="H4" s="29" t="inlineStr">
+      <c r="H4" s="28" t="inlineStr">
         <is>
           <t>Решение</t>
         </is>
@@ -6605,13 +6546,13 @@
           <t>Рация BAOFENG</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="5" t="n">
         <v>1386</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="5" t="n">
         <v>3032</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="5" t="n">
         <v>111</v>
       </c>
       <c r="F5" s="14" t="n">
@@ -6622,37 +6563,37 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Распродать остаток (маржа тонкая)</t>
+          <t>Распродать (маржа тонкая)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n">
+      <c r="A6" s="29" t="n">
         <v>174668134</v>
       </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>Перкуссионный массажёр пистолет</t>
-        </is>
-      </c>
-      <c r="C6" s="31" t="n">
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Перкуссионный массажёр</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="n">
         <v>531</v>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="30" t="n">
         <v>934</v>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="30" t="n">
         <v>-192</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="29" t="n">
         <v>-36</v>
       </c>
-      <c r="G6" s="30" t="n">
+      <c r="G6" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="30" t="inlineStr">
-        <is>
-          <t>НЕ продаём (убыток) — списать/вернуть</t>
+      <c r="H6" s="29" t="inlineStr">
+        <is>
+          <t>НЕ продаём (убыток) — списать</t>
         </is>
       </c>
     </row>
@@ -6665,13 +6606,13 @@
           <t>Триммер для бороды</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="5" t="n">
         <v>263</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="5" t="n">
         <v>848</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="5" t="n">
         <v>92</v>
       </c>
       <c r="F7" s="14" t="n">
@@ -6687,9 +6628,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t>Вывод: электронику выводим из матрицы. Роботы-мойщики — считать отдельно к сезону март-2027.</t>
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>Электронику выводим из матрицы. Роботы-мойщики — считать к сезону март-2027.</t>
         </is>
       </c>
     </row>
